--- a/jogos_2025-05-28.xlsx
+++ b/jogos_2025-05-28.xlsx
@@ -289,27 +289,27 @@
     <t>Dila</t>
   </si>
   <si>
+    <t>Tallinna FC Levadia</t>
+  </si>
+  <si>
     <t>Nõmme Kalju</t>
   </si>
   <si>
-    <t>Tallinna FC Levadia</t>
+    <t>Al Masry</t>
+  </si>
+  <si>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
+    <t>Ceramica Cleopatra</t>
   </si>
   <si>
     <t>Petrojet</t>
   </si>
   <si>
-    <t>Ceramica Cleopatra</t>
-  </si>
-  <si>
-    <t>Al Masry</t>
-  </si>
-  <si>
     <t>Al Ahly</t>
   </si>
   <si>
-    <t>Fredrikstad</t>
-  </si>
-  <si>
     <t>Orlando Pirates</t>
   </si>
   <si>
@@ -325,72 +325,72 @@
     <t>Indy Eleven</t>
   </si>
   <si>
+    <t>DC United</t>
+  </si>
+  <si>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
+    <t>Toronto</t>
+  </si>
+  <si>
+    <t>FC Cincinnati</t>
+  </si>
+  <si>
+    <t>New York RB</t>
+  </si>
+  <si>
+    <t>New York City</t>
+  </si>
+  <si>
     <t>Inter Miami</t>
   </si>
   <si>
-    <t>DC United</t>
-  </si>
-  <si>
-    <t>Toronto</t>
-  </si>
-  <si>
-    <t>New York City</t>
-  </si>
-  <si>
-    <t>Atlanta United FC</t>
-  </si>
-  <si>
-    <t>FC Cincinnati</t>
-  </si>
-  <si>
-    <t>New York RB</t>
-  </si>
-  <si>
     <t>San Antonio</t>
   </si>
   <si>
     <t>Real Monarchs</t>
   </si>
   <si>
+    <t>Columbus Crew</t>
+  </si>
+  <si>
     <t>Minnesota United II</t>
   </si>
   <si>
-    <t>Columbus Crew</t>
-  </si>
-  <si>
     <t>Almirante Brown</t>
   </si>
   <si>
+    <t>Austin</t>
+  </si>
+  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
+    <t>LDU Quito</t>
+  </si>
+  <si>
     <t>Bolívar</t>
   </si>
   <si>
-    <t>LDU Quito</t>
-  </si>
-  <si>
-    <t>Austin</t>
+    <t>Flamengo</t>
   </si>
   <si>
     <t>Palmeiras</t>
   </si>
   <si>
-    <t>Flamengo</t>
-  </si>
-  <si>
     <t>LA Galaxy</t>
   </si>
   <si>
     <t>Las Vegas Lights</t>
   </si>
   <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
     <t>Portland Timbers</t>
   </si>
   <si>
-    <t>Vancouver Whitecaps</t>
-  </si>
-  <si>
     <t>Central Coast II</t>
   </si>
   <si>
@@ -409,27 +409,27 @@
     <t>Dinamo Tbilisi</t>
   </si>
   <si>
+    <t>Vaprus</t>
+  </si>
+  <si>
     <t>Paide</t>
   </si>
   <si>
-    <t>Vaprus</t>
+    <t>Haras El Hodood</t>
+  </si>
+  <si>
+    <t>Rosenborg</t>
+  </si>
+  <si>
+    <t>Pyramids FC</t>
   </si>
   <si>
     <t>National Bank of Egypt</t>
   </si>
   <si>
-    <t>Pyramids FC</t>
-  </si>
-  <si>
-    <t>Haras El Hodood</t>
-  </si>
-  <si>
     <t>Pharco</t>
   </si>
   <si>
-    <t>Rosenborg</t>
-  </si>
-  <si>
     <t>Magesi</t>
   </si>
   <si>
@@ -445,70 +445,70 @@
     <t>Hartford Athletic</t>
   </si>
   <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
+    <t>Orlando City</t>
+  </si>
+  <si>
+    <t>Philadelphia Union</t>
+  </si>
+  <si>
+    <t>FC Dallas</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>Houston Dynamo</t>
+  </si>
+  <si>
     <t>Montreal Impact</t>
   </si>
   <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
-    <t>Philadelphia Union</t>
-  </si>
-  <si>
-    <t>Houston Dynamo</t>
-  </si>
-  <si>
-    <t>Orlando City</t>
-  </si>
-  <si>
-    <t>FC Dallas</t>
-  </si>
-  <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
     <t>Tulsa Roughnecks</t>
   </si>
   <si>
     <t>Portland Timbers II</t>
   </si>
   <si>
+    <t>Nashville SC</t>
+  </si>
+  <si>
     <t>Whitecaps II</t>
   </si>
   <si>
-    <t>Nashville SC</t>
-  </si>
-  <si>
     <t>Nueva Chicago</t>
   </si>
   <si>
+    <t>Real Salt Lake</t>
+  </si>
+  <si>
     <t>San Diego</t>
   </si>
   <si>
+    <t>Central Córdoba SdE</t>
+  </si>
+  <si>
     <t>Cerro Porteño</t>
   </si>
   <si>
-    <t>Central Córdoba SdE</t>
-  </si>
-  <si>
-    <t>Real Salt Lake</t>
+    <t>Deportivo Táchira</t>
   </si>
   <si>
     <t>Sporting Cristal</t>
   </si>
   <si>
-    <t>Deportivo Táchira</t>
-  </si>
-  <si>
     <t>SJ Earthquakes</t>
   </si>
   <si>
     <t>Phoenix Rising</t>
   </si>
   <si>
+    <t>Minnesota United</t>
+  </si>
+  <si>
     <t>Colorado Rapids</t>
-  </si>
-  <si>
-    <t>Minnesota United</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1086,13 +1086,13 @@
         <v>165</v>
       </c>
       <c r="L2">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="M2">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="N2">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="O2">
         <v>1.36</v>
@@ -1134,16 +1134,16 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC2">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AD2">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE2">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AF2">
         <v>0</v>
@@ -1936,91 +1936,91 @@
         <v>165</v>
       </c>
       <c r="L7">
+        <v>1.96</v>
+      </c>
+      <c r="M7">
+        <v>3.35</v>
+      </c>
+      <c r="N7">
+        <v>3.45</v>
+      </c>
+      <c r="O7">
+        <v>1.75</v>
+      </c>
+      <c r="P7">
+        <v>9</v>
+      </c>
+      <c r="Q7">
+        <v>2.4</v>
+      </c>
+      <c r="R7">
+        <v>1.43</v>
+      </c>
+      <c r="S7">
+        <v>2.63</v>
+      </c>
+      <c r="T7">
+        <v>2.85</v>
+      </c>
+      <c r="U7">
+        <v>1.37</v>
+      </c>
+      <c r="V7">
+        <v>7.3</v>
+      </c>
+      <c r="W7">
+        <v>1.06</v>
+      </c>
+      <c r="X7">
+        <v>1.04</v>
+      </c>
+      <c r="Y7">
+        <v>8.5</v>
+      </c>
+      <c r="Z7">
+        <v>1.33</v>
+      </c>
+      <c r="AA7">
+        <v>3</v>
+      </c>
+      <c r="AB7">
+        <v>2</v>
+      </c>
+      <c r="AC7">
+        <v>1.72</v>
+      </c>
+      <c r="AD7">
+        <v>3.6</v>
+      </c>
+      <c r="AE7">
+        <v>1.25</v>
+      </c>
+      <c r="AF7">
+        <v>1.84</v>
+      </c>
+      <c r="AG7">
         <v>1.92</v>
       </c>
-      <c r="M7">
-        <v>3.25</v>
-      </c>
-      <c r="N7">
-        <v>3.35</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>1.98</v>
-      </c>
-      <c r="AC7">
+      <c r="AH7">
+        <v>6.5</v>
+      </c>
+      <c r="AI7">
+        <v>1.08</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>166</v>
+      </c>
+      <c r="AL7">
+        <v>1.27</v>
+      </c>
+      <c r="AM7">
+        <v>1.3</v>
+      </c>
+      <c r="AN7">
         <v>1.65</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>166</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>0</v>
       </c>
       <c r="AO7">
         <v>-1</v>
@@ -2062,10 +2062,10 @@
         <v>0</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD7" s="3">
         <v>45805.54166666666</v>
@@ -2106,76 +2106,76 @@
         <v>165</v>
       </c>
       <c r="L8">
-        <v>2.27</v>
+        <v>1.14</v>
       </c>
       <c r="M8">
+        <v>7</v>
+      </c>
+      <c r="N8">
+        <v>10</v>
+      </c>
+      <c r="O8">
+        <v>1.17</v>
+      </c>
+      <c r="P8">
+        <v>18.5</v>
+      </c>
+      <c r="Q8">
+        <v>5</v>
+      </c>
+      <c r="R8">
+        <v>1.25</v>
+      </c>
+      <c r="S8">
         <v>3.4</v>
       </c>
-      <c r="N8">
-        <v>2.65</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB8">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AC8">
-        <v>2.3</v>
+        <v>2.69</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ8" t="s">
         <v>166</v>
@@ -2184,13 +2184,13 @@
         <v>166</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AO8">
         <v>-1</v>
@@ -2232,10 +2232,10 @@
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BD8" s="3">
         <v>45805.54166666666</v>
@@ -2276,77 +2276,77 @@
         <v>165</v>
       </c>
       <c r="L9">
+        <v>2.44</v>
+      </c>
+      <c r="M9">
+        <v>3.51</v>
+      </c>
+      <c r="N9">
+        <v>2.35</v>
+      </c>
+      <c r="O9">
+        <v>1.8</v>
+      </c>
+      <c r="P9">
+        <v>12.5</v>
+      </c>
+      <c r="Q9">
+        <v>2.1</v>
+      </c>
+      <c r="R9">
+        <v>1.3</v>
+      </c>
+      <c r="S9">
+        <v>3.1</v>
+      </c>
+      <c r="T9">
+        <v>2.36</v>
+      </c>
+      <c r="U9">
+        <v>1.55</v>
+      </c>
+      <c r="V9">
+        <v>5.45</v>
+      </c>
+      <c r="W9">
+        <v>1.14</v>
+      </c>
+      <c r="X9">
+        <v>1.03</v>
+      </c>
+      <c r="Y9">
+        <v>15</v>
+      </c>
+      <c r="Z9">
         <v>1.18</v>
       </c>
-      <c r="M9">
-        <v>5.8</v>
-      </c>
-      <c r="N9">
-        <v>11</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
+      <c r="AA9">
+        <v>4.6</v>
+      </c>
+      <c r="AB9">
+        <v>1.52</v>
+      </c>
+      <c r="AC9">
+        <v>2.37</v>
+      </c>
+      <c r="AD9">
+        <v>2.45</v>
+      </c>
+      <c r="AE9">
+        <v>1.5</v>
+      </c>
+      <c r="AF9">
+        <v>1.5</v>
+      </c>
+      <c r="AG9">
+        <v>2.45</v>
+      </c>
+      <c r="AH9">
+        <v>4</v>
+      </c>
+      <c r="AI9">
         <v>1.2</v>
       </c>
-      <c r="S9">
-        <v>4</v>
-      </c>
-      <c r="T9">
-        <v>1.97</v>
-      </c>
-      <c r="U9">
-        <v>1.74</v>
-      </c>
-      <c r="V9">
-        <v>4.1</v>
-      </c>
-      <c r="W9">
-        <v>1.19</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
-        <v>1.06</v>
-      </c>
-      <c r="AA9">
-        <v>5.8</v>
-      </c>
-      <c r="AB9">
-        <v>1.32</v>
-      </c>
-      <c r="AC9">
-        <v>2.85</v>
-      </c>
-      <c r="AD9">
-        <v>1.9</v>
-      </c>
-      <c r="AE9">
-        <v>1.71</v>
-      </c>
-      <c r="AF9">
-        <v>2.1</v>
-      </c>
-      <c r="AG9">
-        <v>1.55</v>
-      </c>
-      <c r="AH9">
-        <v>3.15</v>
-      </c>
-      <c r="AI9">
-        <v>1.26</v>
-      </c>
       <c r="AJ9" t="s">
         <v>166</v>
       </c>
@@ -2354,13 +2354,13 @@
         <v>166</v>
       </c>
       <c r="AL9">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="AM9">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="AN9">
-        <v>6.1</v>
+        <v>1.6</v>
       </c>
       <c r="AO9">
         <v>-1</v>
@@ -2402,10 +2402,10 @@
         <v>0</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD9" s="3">
         <v>45805.54166666666</v>
@@ -2446,91 +2446,91 @@
         <v>165</v>
       </c>
       <c r="L10">
-        <v>3.45</v>
+        <v>1.6</v>
       </c>
       <c r="M10">
-        <v>2.68</v>
+        <v>3.34</v>
       </c>
       <c r="N10">
-        <v>2.19</v>
+        <v>5.2</v>
       </c>
       <c r="O10">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="P10">
         <v>7</v>
       </c>
       <c r="Q10">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="R10">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S10">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="T10">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U10">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V10">
         <v>8.5</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="Z10">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AA10">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="AB10">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC10">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AD10">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AE10">
+        <v>1.17</v>
+      </c>
+      <c r="AF10">
+        <v>2.35</v>
+      </c>
+      <c r="AG10">
+        <v>1.55</v>
+      </c>
+      <c r="AH10">
+        <v>9</v>
+      </c>
+      <c r="AI10">
+        <v>1.05</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>166</v>
+      </c>
+      <c r="AL10">
+        <v>1.11</v>
+      </c>
+      <c r="AM10">
         <v>1.25</v>
       </c>
-      <c r="AF10">
-        <v>1.75</v>
-      </c>
-      <c r="AG10">
-        <v>1.9</v>
-      </c>
-      <c r="AH10">
-        <v>7</v>
-      </c>
-      <c r="AI10">
-        <v>1.07</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>166</v>
-      </c>
-      <c r="AL10">
-        <v>1.37</v>
-      </c>
-      <c r="AM10">
-        <v>1.35</v>
-      </c>
       <c r="AN10">
-        <v>1.29</v>
+        <v>2.25</v>
       </c>
       <c r="AO10">
         <v>-1</v>
@@ -2572,10 +2572,10 @@
         <v>0</v>
       </c>
       <c r="BB10">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="BC10">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="BD10" s="3">
         <v>45805.58333333334</v>
@@ -2589,10 +2589,10 @@
         <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E11" t="s">
         <v>94</v>
@@ -2616,76 +2616,76 @@
         <v>165</v>
       </c>
       <c r="L11">
-        <v>3.94</v>
+        <v>2.72</v>
       </c>
       <c r="M11">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="N11">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="O11">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="P11">
-        <v>9.25</v>
+        <v>8.25</v>
       </c>
       <c r="Q11">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="R11">
+        <v>1.44</v>
+      </c>
+      <c r="S11">
+        <v>2.63</v>
+      </c>
+      <c r="T11">
+        <v>3</v>
+      </c>
+      <c r="U11">
         <v>1.36</v>
       </c>
-      <c r="S11">
-        <v>2.88</v>
-      </c>
-      <c r="T11">
-        <v>2.7</v>
-      </c>
-      <c r="U11">
-        <v>1.4</v>
-      </c>
       <c r="V11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W11">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y11">
         <v>8.5</v>
       </c>
       <c r="Z11">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AA11">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="AB11">
+        <v>1.86</v>
+      </c>
+      <c r="AC11">
+        <v>1.84</v>
+      </c>
+      <c r="AD11">
+        <v>3.55</v>
+      </c>
+      <c r="AE11">
+        <v>1.28</v>
+      </c>
+      <c r="AF11">
         <v>1.91</v>
-      </c>
-      <c r="AC11">
-        <v>1.79</v>
-      </c>
-      <c r="AD11">
-        <v>3.2</v>
-      </c>
-      <c r="AE11">
-        <v>1.3</v>
-      </c>
-      <c r="AF11">
-        <v>1.8</v>
       </c>
       <c r="AG11">
         <v>1.91</v>
       </c>
       <c r="AH11">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AI11">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AJ11" t="s">
         <v>166</v>
@@ -2694,46 +2694,46 @@
         <v>166</v>
       </c>
       <c r="AL11">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AM11">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AN11">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="AO11">
         <v>-1</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ11">
         <v>0</v>
@@ -2742,10 +2742,10 @@
         <v>0</v>
       </c>
       <c r="BB11">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="BC11">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="BD11" s="3">
         <v>45805.58333333334</v>
@@ -2786,76 +2786,76 @@
         <v>165</v>
       </c>
       <c r="L12">
-        <v>1.6</v>
+        <v>3.94</v>
       </c>
       <c r="M12">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N12">
-        <v>5.2</v>
+        <v>1.78</v>
       </c>
       <c r="O12">
+        <v>2.75</v>
+      </c>
+      <c r="P12">
+        <v>9.25</v>
+      </c>
+      <c r="Q12">
         <v>1.57</v>
       </c>
-      <c r="P12">
-        <v>7</v>
-      </c>
-      <c r="Q12">
-        <v>3.1</v>
-      </c>
       <c r="R12">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="S12">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="T12">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="U12">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z12">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="AA12">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="AB12">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AC12">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AD12">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="AE12">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AF12">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AG12">
-        <v>1.55</v>
+        <v>1.97</v>
       </c>
       <c r="AH12">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AI12">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AJ12" t="s">
         <v>166</v>
@@ -2864,13 +2864,13 @@
         <v>166</v>
       </c>
       <c r="AL12">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AM12">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AN12">
-        <v>2.16</v>
+        <v>1.1</v>
       </c>
       <c r="AO12">
         <v>-1</v>
@@ -2912,10 +2912,10 @@
         <v>0</v>
       </c>
       <c r="BB12">
+        <v>2.75</v>
+      </c>
+      <c r="BC12">
         <v>1.57</v>
-      </c>
-      <c r="BC12">
-        <v>3.1</v>
       </c>
       <c r="BD12" s="3">
         <v>45805.58333333334</v>
@@ -2956,76 +2956,76 @@
         <v>165</v>
       </c>
       <c r="L13">
+        <v>3.45</v>
+      </c>
+      <c r="M13">
+        <v>2.68</v>
+      </c>
+      <c r="N13">
+        <v>2.19</v>
+      </c>
+      <c r="O13">
+        <v>2.4</v>
+      </c>
+      <c r="P13">
+        <v>7</v>
+      </c>
+      <c r="Q13">
+        <v>1.85</v>
+      </c>
+      <c r="R13">
+        <v>1.42</v>
+      </c>
+      <c r="S13">
+        <v>2.47</v>
+      </c>
+      <c r="T13">
+        <v>3</v>
+      </c>
+      <c r="U13">
+        <v>1.33</v>
+      </c>
+      <c r="V13">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W13">
+        <v>1.06</v>
+      </c>
+      <c r="X13">
+        <v>1.03</v>
+      </c>
+      <c r="Y13">
+        <v>7.6</v>
+      </c>
+      <c r="Z13">
+        <v>1.33</v>
+      </c>
+      <c r="AA13">
+        <v>3</v>
+      </c>
+      <c r="AB13">
+        <v>2.05</v>
+      </c>
+      <c r="AC13">
+        <v>1.61</v>
+      </c>
+      <c r="AD13">
+        <v>3.6</v>
+      </c>
+      <c r="AE13">
         <v>1.2</v>
       </c>
-      <c r="M13">
-        <v>5.1</v>
-      </c>
-      <c r="N13">
-        <v>11</v>
-      </c>
-      <c r="O13">
-        <v>1.17</v>
-      </c>
-      <c r="P13">
-        <v>15</v>
-      </c>
-      <c r="Q13">
-        <v>5.15</v>
-      </c>
-      <c r="R13">
-        <v>1.28</v>
-      </c>
-      <c r="S13">
-        <v>3.2</v>
-      </c>
-      <c r="T13">
-        <v>2.4</v>
-      </c>
-      <c r="U13">
-        <v>1.47</v>
-      </c>
-      <c r="V13">
-        <v>6.15</v>
-      </c>
-      <c r="W13">
-        <v>1.12</v>
-      </c>
-      <c r="X13">
-        <v>1.02</v>
-      </c>
-      <c r="Y13">
-        <v>12</v>
-      </c>
-      <c r="Z13">
-        <v>1.17</v>
-      </c>
-      <c r="AA13">
-        <v>4.3</v>
-      </c>
-      <c r="AB13">
-        <v>1.67</v>
-      </c>
-      <c r="AC13">
-        <v>2</v>
-      </c>
-      <c r="AD13">
-        <v>2.45</v>
-      </c>
-      <c r="AE13">
-        <v>1.47</v>
-      </c>
       <c r="AF13">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="AG13">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="AH13">
-        <v>5.05</v>
+        <v>7</v>
       </c>
       <c r="AI13">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AJ13" t="s">
         <v>166</v>
@@ -3034,13 +3034,13 @@
         <v>166</v>
       </c>
       <c r="AL13">
-        <v>1.06</v>
+        <v>1.35</v>
       </c>
       <c r="AM13">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="AN13">
-        <v>4.1</v>
+        <v>1.27</v>
       </c>
       <c r="AO13">
         <v>-1</v>
@@ -3082,10 +3082,10 @@
         <v>0</v>
       </c>
       <c r="BB13">
-        <v>1.17</v>
+        <v>2.4</v>
       </c>
       <c r="BC13">
-        <v>5.15</v>
+        <v>1.85</v>
       </c>
       <c r="BD13" s="3">
         <v>45805.58333333334</v>
@@ -3099,10 +3099,10 @@
         <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E14" t="s">
         <v>97</v>
@@ -3126,124 +3126,124 @@
         <v>165</v>
       </c>
       <c r="L14">
-        <v>2.72</v>
+        <v>1.2</v>
       </c>
       <c r="M14">
-        <v>3.26</v>
+        <v>5.1</v>
       </c>
       <c r="N14">
+        <v>11</v>
+      </c>
+      <c r="O14">
+        <v>1.17</v>
+      </c>
+      <c r="P14">
+        <v>15</v>
+      </c>
+      <c r="Q14">
+        <v>5.15</v>
+      </c>
+      <c r="R14">
+        <v>1.31</v>
+      </c>
+      <c r="S14">
+        <v>3.28</v>
+      </c>
+      <c r="T14">
         <v>2.25</v>
       </c>
-      <c r="O14">
-        <v>2.3</v>
-      </c>
-      <c r="P14">
-        <v>8.25</v>
-      </c>
-      <c r="Q14">
-        <v>1.73</v>
-      </c>
-      <c r="R14">
-        <v>1.44</v>
-      </c>
-      <c r="S14">
-        <v>2.63</v>
-      </c>
-      <c r="T14">
-        <v>3</v>
-      </c>
       <c r="U14">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X14">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="Z14">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AA14">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="AB14">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AC14">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AD14">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="AE14">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="AF14">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AG14">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="AH14">
-        <v>7</v>
+        <v>5.05</v>
       </c>
       <c r="AI14">
+        <v>1.16</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>166</v>
+      </c>
+      <c r="AL14">
+        <v>1.01</v>
+      </c>
+      <c r="AM14">
         <v>1.09</v>
       </c>
-      <c r="AJ14" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK14" t="s">
-        <v>166</v>
-      </c>
-      <c r="AL14">
-        <v>1.6</v>
-      </c>
-      <c r="AM14">
-        <v>1.32</v>
-      </c>
       <c r="AN14">
-        <v>1.35</v>
+        <v>4.45</v>
       </c>
       <c r="AO14">
         <v>-1</v>
       </c>
       <c r="AP14">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AQ14">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AR14">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="AS14">
-        <v>2.19</v>
+        <v>2.55</v>
       </c>
       <c r="AT14">
-        <v>2.88</v>
+        <v>3.32</v>
       </c>
       <c r="AU14">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="AV14">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AW14">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AX14">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AY14">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AZ14">
         <v>0</v>
@@ -3252,10 +3252,10 @@
         <v>0</v>
       </c>
       <c r="BB14">
-        <v>2.3</v>
+        <v>1.17</v>
       </c>
       <c r="BC14">
-        <v>1.73</v>
+        <v>5.15</v>
       </c>
       <c r="BD14" s="3">
         <v>45805.58333333334</v>
@@ -3386,34 +3386,34 @@
         <v>-1</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ15">
         <v>0</v>
@@ -3514,10 +3514,10 @@
         <v>6.25</v>
       </c>
       <c r="AB16">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC16">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AD16">
         <v>1.75</v>
@@ -4006,7 +4006,7 @@
         <v>1.5</v>
       </c>
       <c r="V19">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="W19">
         <v>1.11</v>
@@ -4015,10 +4015,10 @@
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Z19">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AA19">
         <v>3.84</v>
@@ -4030,22 +4030,22 @@
         <v>2.08</v>
       </c>
       <c r="AD19">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AE19">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF19">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG19">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH19">
-        <v>4.95</v>
+        <v>4.75</v>
       </c>
       <c r="AI19">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AJ19" t="s">
         <v>166</v>
@@ -4054,13 +4054,13 @@
         <v>166</v>
       </c>
       <c r="AL19">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AM19">
         <v>1.22</v>
       </c>
       <c r="AN19">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="AO19">
         <v>-1</v>
@@ -4146,76 +4146,76 @@
         <v>165</v>
       </c>
       <c r="L20">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="M20">
+        <v>3.45</v>
+      </c>
+      <c r="N20">
+        <v>3.29</v>
+      </c>
+      <c r="O20">
+        <v>1.67</v>
+      </c>
+      <c r="P20">
+        <v>11.5</v>
+      </c>
+      <c r="Q20">
+        <v>2.25</v>
+      </c>
+      <c r="R20">
+        <v>1.3</v>
+      </c>
+      <c r="S20">
+        <v>3.4</v>
+      </c>
+      <c r="T20">
+        <v>2.5</v>
+      </c>
+      <c r="U20">
+        <v>1.5</v>
+      </c>
+      <c r="V20">
+        <v>6</v>
+      </c>
+      <c r="W20">
+        <v>1.13</v>
+      </c>
+      <c r="X20">
+        <v>1.04</v>
+      </c>
+      <c r="Y20">
+        <v>10</v>
+      </c>
+      <c r="Z20">
+        <v>1.2</v>
+      </c>
+      <c r="AA20">
+        <v>4.33</v>
+      </c>
+      <c r="AB20">
+        <v>1.76</v>
+      </c>
+      <c r="AC20">
+        <v>1.94</v>
+      </c>
+      <c r="AD20">
+        <v>2.55</v>
+      </c>
+      <c r="AE20">
+        <v>1.5</v>
+      </c>
+      <c r="AF20">
+        <v>1.57</v>
+      </c>
+      <c r="AG20">
+        <v>2.25</v>
+      </c>
+      <c r="AH20">
         <v>4.5</v>
       </c>
-      <c r="N20">
-        <v>4.9</v>
-      </c>
-      <c r="O20">
-        <v>1.3</v>
-      </c>
-      <c r="P20">
-        <v>15</v>
-      </c>
-      <c r="Q20">
-        <v>3.4</v>
-      </c>
-      <c r="R20">
-        <v>1.22</v>
-      </c>
-      <c r="S20">
-        <v>4</v>
-      </c>
-      <c r="T20">
-        <v>2.1</v>
-      </c>
-      <c r="U20">
-        <v>1.67</v>
-      </c>
-      <c r="V20">
-        <v>4.5</v>
-      </c>
-      <c r="W20">
-        <v>1.18</v>
-      </c>
-      <c r="X20">
-        <v>1.01</v>
-      </c>
-      <c r="Y20">
-        <v>17</v>
-      </c>
-      <c r="Z20">
-        <v>1.14</v>
-      </c>
-      <c r="AA20">
-        <v>5.5</v>
-      </c>
-      <c r="AB20">
-        <v>1.45</v>
-      </c>
-      <c r="AC20">
-        <v>2.55</v>
-      </c>
-      <c r="AD20">
-        <v>2.15</v>
-      </c>
-      <c r="AE20">
-        <v>1.61</v>
-      </c>
-      <c r="AF20">
-        <v>1.67</v>
-      </c>
-      <c r="AG20">
-        <v>2.1</v>
-      </c>
-      <c r="AH20">
-        <v>3.7</v>
-      </c>
       <c r="AI20">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AJ20" t="s">
         <v>166</v>
@@ -4224,46 +4224,46 @@
         <v>166</v>
       </c>
       <c r="AL20">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="AM20">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AN20">
-        <v>2.65</v>
+        <v>1.62</v>
       </c>
       <c r="AO20">
         <v>-1</v>
       </c>
       <c r="AP20">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AQ20">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR20">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AS20">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="AT20">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="AU20">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="AV20">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="AW20">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="AX20">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AY20">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AZ20">
         <v>0</v>
@@ -4272,10 +4272,10 @@
         <v>0</v>
       </c>
       <c r="BB20">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="BC20">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="BD20" s="3">
         <v>45805.85416666666</v>
@@ -4316,40 +4316,40 @@
         <v>165</v>
       </c>
       <c r="L21">
-        <v>1.9</v>
+        <v>2.39</v>
       </c>
       <c r="M21">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="N21">
-        <v>3.29</v>
+        <v>2.49</v>
       </c>
       <c r="O21">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="P21">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Q21">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="R21">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S21">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T21">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U21">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="W21">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
         <v>1.04</v>
@@ -4367,7 +4367,7 @@
         <v>1.61</v>
       </c>
       <c r="AC21">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD21">
         <v>2.55</v>
@@ -4376,10 +4376,10 @@
         <v>1.5</v>
       </c>
       <c r="AF21">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG21">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH21">
         <v>4.5</v>
@@ -4394,46 +4394,46 @@
         <v>166</v>
       </c>
       <c r="AL21">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AM21">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AN21">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AO21">
         <v>-1</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ21">
         <v>0</v>
@@ -4442,10 +4442,10 @@
         <v>0</v>
       </c>
       <c r="BB21">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BC21">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BD21" s="3">
         <v>45805.85416666666</v>
@@ -4656,64 +4656,64 @@
         <v>165</v>
       </c>
       <c r="L23">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="M23">
-        <v>3.3</v>
+        <v>3.91</v>
       </c>
       <c r="N23">
-        <v>3.57</v>
+        <v>5.1</v>
       </c>
       <c r="O23">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="P23">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="Q23">
+        <v>3</v>
+      </c>
+      <c r="R23">
+        <v>1.33</v>
+      </c>
+      <c r="S23">
+        <v>3.25</v>
+      </c>
+      <c r="T23">
         <v>2.5</v>
       </c>
-      <c r="R23">
-        <v>1.36</v>
-      </c>
-      <c r="S23">
-        <v>3</v>
-      </c>
-      <c r="T23">
-        <v>2.63</v>
-      </c>
       <c r="U23">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z23">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AA23">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AB23">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AC23">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AD23">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AE23">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AF23">
         <v>1.75</v>
@@ -4722,10 +4722,10 @@
         <v>2</v>
       </c>
       <c r="AH23">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AI23">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AJ23" t="s">
         <v>166</v>
@@ -4734,46 +4734,46 @@
         <v>166</v>
       </c>
       <c r="AL23">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AM23">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AN23">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AO23">
         <v>-1</v>
       </c>
       <c r="AP23">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AQ23">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AR23">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AS23">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="AT23">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="AU23">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="AV23">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AW23">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AX23">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AY23">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AZ23">
         <v>0</v>
@@ -4782,10 +4782,10 @@
         <v>0</v>
       </c>
       <c r="BB23">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="BC23">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="BD23" s="3">
         <v>45805.85416666666</v>
@@ -4826,76 +4826,76 @@
         <v>165</v>
       </c>
       <c r="L24">
-        <v>2.39</v>
+        <v>1.8</v>
       </c>
       <c r="M24">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="N24">
-        <v>2.49</v>
+        <v>3.71</v>
       </c>
       <c r="O24">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="P24">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="Q24">
+        <v>2.63</v>
+      </c>
+      <c r="R24">
+        <v>1.36</v>
+      </c>
+      <c r="S24">
+        <v>3</v>
+      </c>
+      <c r="T24">
+        <v>2.63</v>
+      </c>
+      <c r="U24">
+        <v>1.44</v>
+      </c>
+      <c r="V24">
+        <v>7</v>
+      </c>
+      <c r="W24">
+        <v>1.1</v>
+      </c>
+      <c r="X24">
+        <v>1.05</v>
+      </c>
+      <c r="Y24">
+        <v>9.5</v>
+      </c>
+      <c r="Z24">
+        <v>1.28</v>
+      </c>
+      <c r="AA24">
+        <v>3.6</v>
+      </c>
+      <c r="AB24">
+        <v>1.81</v>
+      </c>
+      <c r="AC24">
+        <v>1.89</v>
+      </c>
+      <c r="AD24">
+        <v>3.1</v>
+      </c>
+      <c r="AE24">
+        <v>1.35</v>
+      </c>
+      <c r="AF24">
+        <v>1.75</v>
+      </c>
+      <c r="AG24">
         <v>2</v>
       </c>
-      <c r="R24">
-        <v>1.29</v>
-      </c>
-      <c r="S24">
-        <v>3.5</v>
-      </c>
-      <c r="T24">
-        <v>2.38</v>
-      </c>
-      <c r="U24">
-        <v>1.53</v>
-      </c>
-      <c r="V24">
-        <v>5.5</v>
-      </c>
-      <c r="W24">
-        <v>1.14</v>
-      </c>
-      <c r="X24">
-        <v>1.04</v>
-      </c>
-      <c r="Y24">
-        <v>10</v>
-      </c>
-      <c r="Z24">
-        <v>1.2</v>
-      </c>
-      <c r="AA24">
-        <v>4.33</v>
-      </c>
-      <c r="AB24">
-        <v>1.61</v>
-      </c>
-      <c r="AC24">
-        <v>2.2</v>
-      </c>
-      <c r="AD24">
-        <v>2.55</v>
-      </c>
-      <c r="AE24">
-        <v>1.5</v>
-      </c>
-      <c r="AF24">
-        <v>1.53</v>
-      </c>
-      <c r="AG24">
-        <v>2.38</v>
-      </c>
       <c r="AH24">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="AI24">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AJ24" t="s">
         <v>166</v>
@@ -4904,58 +4904,58 @@
         <v>166</v>
       </c>
       <c r="AL24">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="AM24">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AN24">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AO24">
         <v>-1</v>
       </c>
       <c r="AP24">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AQ24">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AR24">
+        <v>1.92</v>
+      </c>
+      <c r="AS24">
+        <v>2.43</v>
+      </c>
+      <c r="AT24">
+        <v>3.15</v>
+      </c>
+      <c r="AU24">
+        <v>2.95</v>
+      </c>
+      <c r="AV24">
+        <v>2.23</v>
+      </c>
+      <c r="AW24">
         <v>1.77</v>
       </c>
-      <c r="AS24">
-        <v>2.23</v>
-      </c>
-      <c r="AT24">
-        <v>2.9</v>
-      </c>
-      <c r="AU24">
-        <v>3.3</v>
-      </c>
-      <c r="AV24">
-        <v>2.43</v>
-      </c>
-      <c r="AW24">
-        <v>1.91</v>
-      </c>
       <c r="AX24">
+        <v>1.47</v>
+      </c>
+      <c r="AY24">
+        <v>1.29</v>
+      </c>
+      <c r="AZ24">
+        <v>0</v>
+      </c>
+      <c r="BA24">
+        <v>0</v>
+      </c>
+      <c r="BB24">
         <v>1.57</v>
       </c>
-      <c r="AY24">
-        <v>1.35</v>
-      </c>
-      <c r="AZ24">
-        <v>0</v>
-      </c>
-      <c r="BA24">
-        <v>0</v>
-      </c>
-      <c r="BB24">
-        <v>1.8</v>
-      </c>
       <c r="BC24">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="BD24" s="3">
         <v>45805.85416666666</v>
@@ -4996,64 +4996,64 @@
         <v>165</v>
       </c>
       <c r="L25">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="M25">
-        <v>3.91</v>
+        <v>3.3</v>
       </c>
       <c r="N25">
-        <v>5.1</v>
+        <v>3.57</v>
       </c>
       <c r="O25">
+        <v>1.57</v>
+      </c>
+      <c r="P25">
+        <v>9.5</v>
+      </c>
+      <c r="Q25">
+        <v>2.5</v>
+      </c>
+      <c r="R25">
+        <v>1.36</v>
+      </c>
+      <c r="S25">
+        <v>3</v>
+      </c>
+      <c r="T25">
+        <v>2.63</v>
+      </c>
+      <c r="U25">
         <v>1.44</v>
       </c>
-      <c r="P25">
-        <v>11</v>
-      </c>
-      <c r="Q25">
-        <v>3</v>
-      </c>
-      <c r="R25">
-        <v>1.33</v>
-      </c>
-      <c r="S25">
-        <v>3.25</v>
-      </c>
-      <c r="T25">
-        <v>2.5</v>
-      </c>
-      <c r="U25">
-        <v>1.5</v>
-      </c>
       <c r="V25">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W25">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z25">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AA25">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="AB25">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AC25">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AD25">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AE25">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AF25">
         <v>1.75</v>
@@ -5062,10 +5062,10 @@
         <v>2</v>
       </c>
       <c r="AH25">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AI25">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AJ25" t="s">
         <v>166</v>
@@ -5074,46 +5074,46 @@
         <v>166</v>
       </c>
       <c r="AL25">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AM25">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AN25">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AO25">
         <v>-1</v>
       </c>
       <c r="AP25">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU25">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV25">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX25">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY25">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ25">
         <v>0</v>
@@ -5122,10 +5122,10 @@
         <v>0</v>
       </c>
       <c r="BB25">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="BC25">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BD25" s="3">
         <v>45805.85416666666</v>
@@ -5166,124 +5166,124 @@
         <v>165</v>
       </c>
       <c r="L26">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="M26">
-        <v>3.38</v>
+        <v>4.5</v>
       </c>
       <c r="N26">
-        <v>3.71</v>
+        <v>4.9</v>
       </c>
       <c r="O26">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="P26">
-        <v>9.5</v>
+        <v>15</v>
       </c>
       <c r="Q26">
+        <v>3.4</v>
+      </c>
+      <c r="R26">
+        <v>1.22</v>
+      </c>
+      <c r="S26">
+        <v>4</v>
+      </c>
+      <c r="T26">
+        <v>2.1</v>
+      </c>
+      <c r="U26">
+        <v>1.67</v>
+      </c>
+      <c r="V26">
+        <v>4.5</v>
+      </c>
+      <c r="W26">
+        <v>1.18</v>
+      </c>
+      <c r="X26">
+        <v>1.01</v>
+      </c>
+      <c r="Y26">
+        <v>17</v>
+      </c>
+      <c r="Z26">
+        <v>1.14</v>
+      </c>
+      <c r="AA26">
+        <v>5.5</v>
+      </c>
+      <c r="AB26">
+        <v>1.45</v>
+      </c>
+      <c r="AC26">
         <v>2.63</v>
       </c>
-      <c r="R26">
-        <v>1.36</v>
-      </c>
-      <c r="S26">
-        <v>3</v>
-      </c>
-      <c r="T26">
-        <v>2.63</v>
-      </c>
-      <c r="U26">
-        <v>1.44</v>
-      </c>
-      <c r="V26">
-        <v>7</v>
-      </c>
-      <c r="W26">
-        <v>1.1</v>
-      </c>
-      <c r="X26">
-        <v>1.05</v>
-      </c>
-      <c r="Y26">
-        <v>9.5</v>
-      </c>
-      <c r="Z26">
-        <v>1.28</v>
-      </c>
-      <c r="AA26">
-        <v>3.6</v>
-      </c>
-      <c r="AB26">
-        <v>1.81</v>
-      </c>
-      <c r="AC26">
-        <v>1.89</v>
-      </c>
       <c r="AD26">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="AE26">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="AF26">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH26">
-        <v>5.75</v>
+        <v>3.7</v>
       </c>
       <c r="AI26">
+        <v>1.25</v>
+      </c>
+      <c r="AJ26" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>166</v>
+      </c>
+      <c r="AL26">
         <v>1.12</v>
       </c>
-      <c r="AJ26" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK26" t="s">
-        <v>166</v>
-      </c>
-      <c r="AL26">
-        <v>1.24</v>
-      </c>
       <c r="AM26">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AN26">
-        <v>1.88</v>
+        <v>2.65</v>
       </c>
       <c r="AO26">
         <v>-1</v>
       </c>
       <c r="AP26">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AQ26">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AR26">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="AS26">
-        <v>2.43</v>
+        <v>2.04</v>
       </c>
       <c r="AT26">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="AU26">
-        <v>2.95</v>
+        <v>3.65</v>
       </c>
       <c r="AV26">
-        <v>2.23</v>
+        <v>2.65</v>
       </c>
       <c r="AW26">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="AX26">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="AY26">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AZ26">
         <v>0</v>
@@ -5292,10 +5292,10 @@
         <v>0</v>
       </c>
       <c r="BB26">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="BC26">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="BD26" s="3">
         <v>45805.85416666666</v>
@@ -5354,34 +5354,34 @@
         <v>2.5</v>
       </c>
       <c r="R27">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S27">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T27">
         <v>2.8</v>
       </c>
       <c r="U27">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="V27">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="W27">
         <v>1.08</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z27">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AA27">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB27">
         <v>2</v>
@@ -5393,19 +5393,19 @@
         <v>3.3</v>
       </c>
       <c r="AE27">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AF27">
         <v>1.8</v>
       </c>
       <c r="AG27">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AH27">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AI27">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AJ27" t="s">
         <v>166</v>
@@ -5420,7 +5420,7 @@
         <v>0</v>
       </c>
       <c r="AN27">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AO27">
         <v>-1</v>
@@ -5649,7 +5649,7 @@
         <v>65</v>
       </c>
       <c r="C29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D29" t="s">
         <v>83</v>
@@ -5676,76 +5676,76 @@
         <v>165</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ29" t="s">
         <v>166</v>
@@ -5754,46 +5754,46 @@
         <v>166</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO29">
         <v>-1</v>
       </c>
       <c r="AP29">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU29">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AV29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW29">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX29">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY29">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ29">
         <v>0</v>
@@ -5802,10 +5802,10 @@
         <v>0</v>
       </c>
       <c r="BB29">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BC29">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BD29" s="3">
         <v>45805.875</v>
@@ -5819,7 +5819,7 @@
         <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D30" t="s">
         <v>83</v>
@@ -5846,76 +5846,76 @@
         <v>165</v>
       </c>
       <c r="L30">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N30">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W30">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X30">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z30">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH30">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AI30">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="s">
         <v>166</v>
@@ -5924,13 +5924,13 @@
         <v>166</v>
       </c>
       <c r="AL30">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AM30">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN30">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO30">
         <v>-1</v>
@@ -5972,10 +5972,10 @@
         <v>0</v>
       </c>
       <c r="BB30">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BC30">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="BD30" s="3">
         <v>45805.875</v>
@@ -6016,13 +6016,13 @@
         <v>165</v>
       </c>
       <c r="L31">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="M31">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="N31">
-        <v>3.1</v>
+        <v>3.53</v>
       </c>
       <c r="O31">
         <v>2</v>
@@ -6037,55 +6037,55 @@
         <v>1.7</v>
       </c>
       <c r="S31">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="T31">
         <v>3.8</v>
       </c>
       <c r="U31">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W31">
         <v>1.02</v>
       </c>
       <c r="X31">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y31">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="Z31">
         <v>1.6</v>
       </c>
       <c r="AA31">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB31">
         <v>2.88</v>
       </c>
       <c r="AC31">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AD31">
-        <v>5.5</v>
+        <v>6.22</v>
       </c>
       <c r="AE31">
         <v>1.11</v>
       </c>
       <c r="AF31">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AG31">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AH31">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ31" t="s">
         <v>166</v>
@@ -6094,13 +6094,13 @@
         <v>166</v>
       </c>
       <c r="AL31">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AM31">
         <v>1.4</v>
       </c>
       <c r="AN31">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AO31">
         <v>-1</v>
@@ -6186,76 +6186,76 @@
         <v>165</v>
       </c>
       <c r="L32">
-        <v>1.82</v>
+        <v>2.01</v>
       </c>
       <c r="M32">
+        <v>3.33</v>
+      </c>
+      <c r="N32">
+        <v>3.12</v>
+      </c>
+      <c r="O32">
+        <v>1.67</v>
+      </c>
+      <c r="P32">
+        <v>9</v>
+      </c>
+      <c r="Q32">
+        <v>2.4</v>
+      </c>
+      <c r="R32">
+        <v>1.36</v>
+      </c>
+      <c r="S32">
+        <v>3</v>
+      </c>
+      <c r="T32">
+        <v>2.75</v>
+      </c>
+      <c r="U32">
+        <v>1.4</v>
+      </c>
+      <c r="V32">
+        <v>7</v>
+      </c>
+      <c r="W32">
+        <v>1.1</v>
+      </c>
+      <c r="X32">
+        <v>1.06</v>
+      </c>
+      <c r="Y32">
+        <v>8.5</v>
+      </c>
+      <c r="Z32">
+        <v>1.3</v>
+      </c>
+      <c r="AA32">
+        <v>3.4</v>
+      </c>
+      <c r="AB32">
+        <v>1.86</v>
+      </c>
+      <c r="AC32">
+        <v>1.84</v>
+      </c>
+      <c r="AD32">
         <v>3.35</v>
       </c>
-      <c r="N32">
-        <v>3.68</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
-      <c r="Q32">
-        <v>0</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32">
-        <v>0</v>
-      </c>
-      <c r="W32">
-        <v>0</v>
-      </c>
-      <c r="X32">
-        <v>0</v>
-      </c>
-      <c r="Y32">
-        <v>0</v>
-      </c>
-      <c r="Z32">
-        <v>0</v>
-      </c>
-      <c r="AA32">
-        <v>0</v>
-      </c>
-      <c r="AB32">
-        <v>1.83</v>
-      </c>
-      <c r="AC32">
-        <v>1.87</v>
-      </c>
-      <c r="AD32">
-        <v>0</v>
-      </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI32">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ32" t="s">
         <v>166</v>
@@ -6264,46 +6264,46 @@
         <v>166</v>
       </c>
       <c r="AL32">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AM32">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN32">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO32">
         <v>-1</v>
       </c>
       <c r="AP32">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AU32">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV32">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AW32">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AX32">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY32">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ32">
         <v>0</v>
@@ -6312,10 +6312,10 @@
         <v>0</v>
       </c>
       <c r="BB32">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BC32">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD32" s="3">
         <v>45805.89583333334</v>
@@ -6329,7 +6329,7 @@
         <v>67</v>
       </c>
       <c r="C33" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D33" t="s">
         <v>83</v>
@@ -6356,76 +6356,76 @@
         <v>165</v>
       </c>
       <c r="L33">
-        <v>1.32</v>
+        <v>1.82</v>
       </c>
       <c r="M33">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="N33">
-        <v>6.4</v>
+        <v>3.68</v>
       </c>
       <c r="O33">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W33">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y33">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="Z33">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AC33">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AD33">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH33">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AI33">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="s">
         <v>166</v>
@@ -6434,46 +6434,46 @@
         <v>166</v>
       </c>
       <c r="AL33">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AM33">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN33">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AO33">
         <v>-1</v>
       </c>
       <c r="AP33">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ33">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR33">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS33">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AT33">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU33">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV33">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW33">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AX33">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AY33">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AZ33">
         <v>0</v>
@@ -6482,10 +6482,10 @@
         <v>0</v>
       </c>
       <c r="BB33">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC33">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BD33" s="3">
         <v>45805.89583333334</v>
@@ -6669,7 +6669,7 @@
         <v>67</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D35" t="s">
         <v>83</v>
@@ -6696,76 +6696,76 @@
         <v>165</v>
       </c>
       <c r="L35">
-        <v>2.01</v>
+        <v>1.32</v>
       </c>
       <c r="M35">
-        <v>3.33</v>
+        <v>4.9</v>
       </c>
       <c r="N35">
-        <v>3.12</v>
+        <v>6.4</v>
       </c>
       <c r="O35">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="P35">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q35">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="R35">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S35">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="T35">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="U35">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V35">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="W35">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X35">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>8.5</v>
+        <v>14.3</v>
       </c>
       <c r="Z35">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AA35">
-        <v>3.4</v>
+        <v>4.55</v>
       </c>
       <c r="AB35">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="AC35">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AD35">
-        <v>3.35</v>
+        <v>2.58</v>
       </c>
       <c r="AE35">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AF35">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG35">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH35">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="AI35">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AJ35" t="s">
         <v>166</v>
@@ -6774,46 +6774,46 @@
         <v>166</v>
       </c>
       <c r="AL35">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="AM35">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AN35">
-        <v>1.75</v>
+        <v>2.95</v>
       </c>
       <c r="AO35">
         <v>-1</v>
       </c>
       <c r="AP35">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU35">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV35">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW35">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX35">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AY35">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AZ35">
         <v>0</v>
@@ -6822,10 +6822,10 @@
         <v>0</v>
       </c>
       <c r="BB35">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="BC35">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="BD35" s="3">
         <v>45805.89583333334</v>
@@ -6866,76 +6866,76 @@
         <v>165</v>
       </c>
       <c r="L36">
+        <v>1.02</v>
+      </c>
+      <c r="M36">
+        <v>12</v>
+      </c>
+      <c r="N36">
+        <v>17</v>
+      </c>
+      <c r="O36">
+        <v>1.11</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>6.5</v>
+      </c>
+      <c r="R36">
         <v>1.17</v>
       </c>
-      <c r="M36">
-        <v>5.6</v>
-      </c>
-      <c r="N36">
-        <v>11</v>
-      </c>
-      <c r="O36">
-        <v>1.17</v>
-      </c>
-      <c r="P36">
-        <v>13.5</v>
-      </c>
-      <c r="Q36">
-        <v>6</v>
-      </c>
-      <c r="R36">
+      <c r="S36">
+        <v>5</v>
+      </c>
+      <c r="T36">
+        <v>1.8</v>
+      </c>
+      <c r="U36">
+        <v>1.91</v>
+      </c>
+      <c r="V36">
+        <v>3.5</v>
+      </c>
+      <c r="W36">
         <v>1.29</v>
       </c>
-      <c r="S36">
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>1.25</v>
+      </c>
+      <c r="AC36">
         <v>3.5</v>
       </c>
-      <c r="T36">
-        <v>2.38</v>
-      </c>
-      <c r="U36">
-        <v>1.53</v>
-      </c>
-      <c r="V36">
-        <v>5.5</v>
-      </c>
-      <c r="W36">
-        <v>1.14</v>
-      </c>
-      <c r="X36">
-        <v>1.03</v>
-      </c>
-      <c r="Y36">
-        <v>13.8</v>
-      </c>
-      <c r="Z36">
-        <v>1.17</v>
-      </c>
-      <c r="AA36">
-        <v>4.2</v>
-      </c>
-      <c r="AB36">
-        <v>1.57</v>
-      </c>
-      <c r="AC36">
-        <v>2.15</v>
-      </c>
       <c r="AD36">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="AE36">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="AF36">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AG36">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AH36">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI36">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="s">
         <v>166</v>
@@ -6944,46 +6944,46 @@
         <v>166</v>
       </c>
       <c r="AL36">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AM36">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN36">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AO36">
         <v>-1</v>
       </c>
       <c r="AP36">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ36">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR36">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AS36">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT36">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU36">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AV36">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AW36">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AX36">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY36">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ36">
         <v>0</v>
@@ -6992,10 +6992,10 @@
         <v>0</v>
       </c>
       <c r="BB36">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BC36">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="BD36" s="3">
         <v>45805.89583333334</v>
@@ -7036,124 +7036,124 @@
         <v>165</v>
       </c>
       <c r="L37">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="M37">
-        <v>12</v>
+        <v>5.6</v>
       </c>
       <c r="N37">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="O37">
+        <v>1.17</v>
+      </c>
+      <c r="P37">
+        <v>13.5</v>
+      </c>
+      <c r="Q37">
+        <v>6</v>
+      </c>
+      <c r="R37">
+        <v>1.29</v>
+      </c>
+      <c r="S37">
+        <v>3.5</v>
+      </c>
+      <c r="T37">
+        <v>2.38</v>
+      </c>
+      <c r="U37">
+        <v>1.53</v>
+      </c>
+      <c r="V37">
+        <v>5.5</v>
+      </c>
+      <c r="W37">
+        <v>1.14</v>
+      </c>
+      <c r="X37">
+        <v>1.03</v>
+      </c>
+      <c r="Y37">
+        <v>13.8</v>
+      </c>
+      <c r="Z37">
+        <v>1.17</v>
+      </c>
+      <c r="AA37">
+        <v>4.2</v>
+      </c>
+      <c r="AB37">
+        <v>1.57</v>
+      </c>
+      <c r="AC37">
+        <v>2.15</v>
+      </c>
+      <c r="AD37">
+        <v>2.75</v>
+      </c>
+      <c r="AE37">
+        <v>1.45</v>
+      </c>
+      <c r="AF37">
+        <v>2.38</v>
+      </c>
+      <c r="AG37">
+        <v>1.53</v>
+      </c>
+      <c r="AH37">
+        <v>4.2</v>
+      </c>
+      <c r="AI37">
+        <v>1.16</v>
+      </c>
+      <c r="AJ37" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK37" t="s">
+        <v>166</v>
+      </c>
+      <c r="AL37">
+        <v>1.03</v>
+      </c>
+      <c r="AM37">
         <v>1.11</v>
       </c>
-      <c r="P37">
-        <v>0</v>
-      </c>
-      <c r="Q37">
-        <v>6.5</v>
-      </c>
-      <c r="R37">
-        <v>1.17</v>
-      </c>
-      <c r="S37">
-        <v>5</v>
-      </c>
-      <c r="T37">
-        <v>1.8</v>
-      </c>
-      <c r="U37">
-        <v>1.91</v>
-      </c>
-      <c r="V37">
-        <v>3.5</v>
-      </c>
-      <c r="W37">
-        <v>1.29</v>
-      </c>
-      <c r="X37">
-        <v>0</v>
-      </c>
-      <c r="Y37">
-        <v>0</v>
-      </c>
-      <c r="Z37">
-        <v>0</v>
-      </c>
-      <c r="AA37">
-        <v>0</v>
-      </c>
-      <c r="AB37">
-        <v>1.25</v>
-      </c>
-      <c r="AC37">
-        <v>3.5</v>
-      </c>
-      <c r="AD37">
-        <v>1.85</v>
-      </c>
-      <c r="AE37">
-        <v>1.85</v>
-      </c>
-      <c r="AF37">
-        <v>2.63</v>
-      </c>
-      <c r="AG37">
-        <v>1.44</v>
-      </c>
-      <c r="AH37">
-        <v>0</v>
-      </c>
-      <c r="AI37">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK37" t="s">
-        <v>166</v>
-      </c>
-      <c r="AL37">
-        <v>0</v>
-      </c>
-      <c r="AM37">
-        <v>0</v>
-      </c>
       <c r="AN37">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AO37">
         <v>-1</v>
       </c>
       <c r="AP37">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU37">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AV37">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW37">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX37">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY37">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ37">
         <v>0</v>
@@ -7162,10 +7162,10 @@
         <v>0</v>
       </c>
       <c r="BB37">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="BC37">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="BD37" s="3">
         <v>45805.89583333334</v>
@@ -7394,10 +7394,10 @@
         <v>2.2</v>
       </c>
       <c r="R39">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S39">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="T39">
         <v>2.65</v>
@@ -7406,22 +7406,22 @@
         <v>1.4</v>
       </c>
       <c r="V39">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="W39">
         <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y39">
-        <v>9.449999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z39">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AA39">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AB39">
         <v>1.95</v>
@@ -7430,19 +7430,19 @@
         <v>1.85</v>
       </c>
       <c r="AD39">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="AE39">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AF39">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG39">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH39">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AI39">
         <v>1.1</v>
@@ -7454,13 +7454,13 @@
         <v>166</v>
       </c>
       <c r="AL39">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AM39">
         <v>1.27</v>
       </c>
       <c r="AN39">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="AO39">
         <v>-1</v>
@@ -7546,76 +7546,76 @@
         <v>165</v>
       </c>
       <c r="L40">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="M40">
-        <v>3.95</v>
+        <v>3.32</v>
       </c>
       <c r="N40">
-        <v>4.2</v>
+        <v>3.41</v>
       </c>
       <c r="O40">
+        <v>1.62</v>
+      </c>
+      <c r="P40">
+        <v>9.75</v>
+      </c>
+      <c r="Q40">
+        <v>2.5</v>
+      </c>
+      <c r="R40">
+        <v>1.36</v>
+      </c>
+      <c r="S40">
+        <v>3</v>
+      </c>
+      <c r="T40">
+        <v>2.63</v>
+      </c>
+      <c r="U40">
         <v>1.44</v>
       </c>
-      <c r="P40">
-        <v>14.5</v>
-      </c>
-      <c r="Q40">
-        <v>2.75</v>
-      </c>
-      <c r="R40">
+      <c r="V40">
+        <v>7</v>
+      </c>
+      <c r="W40">
+        <v>1.1</v>
+      </c>
+      <c r="X40">
+        <v>1.05</v>
+      </c>
+      <c r="Y40">
+        <v>9.5</v>
+      </c>
+      <c r="Z40">
         <v>1.25</v>
       </c>
-      <c r="S40">
-        <v>3.75</v>
-      </c>
-      <c r="T40">
-        <v>2.1</v>
-      </c>
-      <c r="U40">
-        <v>1.67</v>
-      </c>
-      <c r="V40">
-        <v>5</v>
-      </c>
-      <c r="W40">
-        <v>1.17</v>
-      </c>
-      <c r="X40">
-        <v>1.01</v>
-      </c>
-      <c r="Y40">
-        <v>17</v>
-      </c>
-      <c r="Z40">
-        <v>1.15</v>
-      </c>
       <c r="AA40">
-        <v>5.25</v>
+        <v>3.7</v>
       </c>
       <c r="AB40">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AC40">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AD40">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="AE40">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AF40">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AG40">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AH40">
-        <v>3.7</v>
+        <v>5.75</v>
       </c>
       <c r="AI40">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AJ40" t="s">
         <v>166</v>
@@ -7624,46 +7624,46 @@
         <v>166</v>
       </c>
       <c r="AL40">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AM40">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AN40">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AO40">
         <v>-1</v>
       </c>
       <c r="AP40">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AQ40">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AR40">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AS40">
-        <v>2.32</v>
+        <v>1.98</v>
       </c>
       <c r="AT40">
-        <v>2.95</v>
+        <v>2.48</v>
       </c>
       <c r="AU40">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="AV40">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="AW40">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="AX40">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AY40">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AZ40">
         <v>0</v>
@@ -7672,10 +7672,10 @@
         <v>0</v>
       </c>
       <c r="BB40">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="BC40">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="BD40" s="3">
         <v>45805.97916666666</v>
@@ -7716,77 +7716,77 @@
         <v>165</v>
       </c>
       <c r="L41">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="M41">
-        <v>3.32</v>
+        <v>3.95</v>
       </c>
       <c r="N41">
-        <v>3.41</v>
+        <v>4.2</v>
       </c>
       <c r="O41">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="P41">
-        <v>9.75</v>
+        <v>14.5</v>
       </c>
       <c r="Q41">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="R41">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S41">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="T41">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="U41">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="V41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W41">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X41">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>9.5</v>
+        <v>17</v>
       </c>
       <c r="Z41">
+        <v>1.15</v>
+      </c>
+      <c r="AA41">
+        <v>5.25</v>
+      </c>
+      <c r="AB41">
+        <v>1.5</v>
+      </c>
+      <c r="AC41">
+        <v>2.4</v>
+      </c>
+      <c r="AD41">
+        <v>2.15</v>
+      </c>
+      <c r="AE41">
+        <v>1.61</v>
+      </c>
+      <c r="AF41">
+        <v>1.53</v>
+      </c>
+      <c r="AG41">
+        <v>2.38</v>
+      </c>
+      <c r="AH41">
+        <v>3.7</v>
+      </c>
+      <c r="AI41">
         <v>1.25</v>
       </c>
-      <c r="AA41">
-        <v>3.7</v>
-      </c>
-      <c r="AB41">
-        <v>1.8</v>
-      </c>
-      <c r="AC41">
-        <v>1.9</v>
-      </c>
-      <c r="AD41">
-        <v>3.1</v>
-      </c>
-      <c r="AE41">
-        <v>1.36</v>
-      </c>
-      <c r="AF41">
-        <v>1.75</v>
-      </c>
-      <c r="AG41">
-        <v>2</v>
-      </c>
-      <c r="AH41">
-        <v>5.75</v>
-      </c>
-      <c r="AI41">
-        <v>1.12</v>
-      </c>
       <c r="AJ41" t="s">
         <v>166</v>
       </c>
@@ -7794,58 +7794,58 @@
         <v>166</v>
       </c>
       <c r="AL41">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AM41">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AN41">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AO41">
         <v>-1</v>
       </c>
       <c r="AP41">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AQ41">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AR41">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AS41">
-        <v>1.98</v>
+        <v>2.32</v>
       </c>
       <c r="AT41">
-        <v>2.48</v>
+        <v>2.95</v>
       </c>
       <c r="AU41">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="AV41">
+        <v>2.33</v>
+      </c>
+      <c r="AW41">
+        <v>1.84</v>
+      </c>
+      <c r="AX41">
+        <v>1.53</v>
+      </c>
+      <c r="AY41">
+        <v>1.33</v>
+      </c>
+      <c r="AZ41">
+        <v>0</v>
+      </c>
+      <c r="BA41">
+        <v>0</v>
+      </c>
+      <c r="BB41">
+        <v>1.44</v>
+      </c>
+      <c r="BC41">
         <v>2.75</v>
-      </c>
-      <c r="AW41">
-        <v>2.14</v>
-      </c>
-      <c r="AX41">
-        <v>1.72</v>
-      </c>
-      <c r="AY41">
-        <v>1.47</v>
-      </c>
-      <c r="AZ41">
-        <v>0</v>
-      </c>
-      <c r="BA41">
-        <v>0</v>
-      </c>
-      <c r="BB41">
-        <v>1.62</v>
-      </c>
-      <c r="BC41">
-        <v>2.5</v>
       </c>
       <c r="BD41" s="3">
         <v>45805.97916666666</v>

--- a/jogos_2025-05-28.xlsx
+++ b/jogos_2025-05-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="169">
   <si>
     <t>Date</t>
   </si>
@@ -235,12 +235,12 @@
     <t>Japan J1 League</t>
   </si>
   <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
@@ -274,244 +274,250 @@
     <t>Sydney Olympic</t>
   </si>
   <si>
+    <t>Sangju Sangmu</t>
+  </si>
+  <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Gangwon</t>
   </si>
   <si>
     <t>Urawa Reds</t>
   </si>
   <si>
-    <t>Gwangju</t>
-  </si>
-  <si>
-    <t>Sangju Sangmu</t>
+    <t>Nõmme Kalju</t>
+  </si>
+  <si>
+    <t>Tallinna FC Levadia</t>
   </si>
   <si>
     <t>Dila</t>
   </si>
   <si>
-    <t>Tallinna FC Levadia</t>
-  </si>
-  <si>
-    <t>Nõmme Kalju</t>
+    <t>Al Ahly</t>
   </si>
   <si>
     <t>Al Masry</t>
   </si>
   <si>
+    <t>Petrojet</t>
+  </si>
+  <si>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
     <t>Fredrikstad</t>
   </si>
   <si>
-    <t>Ceramica Cleopatra</t>
-  </si>
-  <si>
-    <t>Petrojet</t>
-  </si>
-  <si>
-    <t>Al Ahly</t>
-  </si>
-  <si>
     <t>Orlando Pirates</t>
   </si>
   <si>
     <t>FK Bodo - Glimt</t>
   </si>
   <si>
+    <t>Nacional</t>
+  </si>
+  <si>
     <t>Internacional</t>
   </si>
   <si>
-    <t>Nacional</t>
-  </si>
-  <si>
     <t>Indy Eleven</t>
   </si>
   <si>
+    <t>FC Cincinnati</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
+    <t>New York RB</t>
+  </si>
+  <si>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
+    <t>New York City</t>
+  </si>
+  <si>
     <t>DC United</t>
   </si>
   <si>
-    <t>Atlanta United FC</t>
-  </si>
-  <si>
     <t>Toronto</t>
   </si>
   <si>
-    <t>FC Cincinnati</t>
-  </si>
-  <si>
-    <t>New York RB</t>
-  </si>
-  <si>
-    <t>New York City</t>
-  </si>
-  <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
     <t>San Antonio</t>
   </si>
   <si>
     <t>Real Monarchs</t>
   </si>
   <si>
+    <t>Minnesota United II</t>
+  </si>
+  <si>
     <t>Columbus Crew</t>
   </si>
   <si>
-    <t>Minnesota United II</t>
-  </si>
-  <si>
     <t>Almirante Brown</t>
   </si>
   <si>
+    <t>LDU Quito</t>
+  </si>
+  <si>
+    <t>Bolívar</t>
+  </si>
+  <si>
+    <t>Seattle Sounders</t>
+  </si>
+  <si>
     <t>Austin</t>
   </si>
   <si>
-    <t>Seattle Sounders</t>
-  </si>
-  <si>
-    <t>LDU Quito</t>
-  </si>
-  <si>
-    <t>Bolívar</t>
+    <t>Palmeiras</t>
   </si>
   <si>
     <t>Flamengo</t>
   </si>
   <si>
-    <t>Palmeiras</t>
-  </si>
-  <si>
     <t>LA Galaxy</t>
   </si>
   <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
     <t>Las Vegas Lights</t>
   </si>
   <si>
-    <t>Vancouver Whitecaps</t>
-  </si>
-  <si>
     <t>Portland Timbers</t>
   </si>
   <si>
     <t>Central Coast II</t>
   </si>
   <si>
+    <t>FC Seoul</t>
+  </si>
+  <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
     <t>Anyang</t>
   </si>
   <si>
     <t>Cerezo Osaka</t>
   </si>
   <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
-    <t>FC Seoul</t>
+    <t>Paide</t>
+  </si>
+  <si>
+    <t>Vaprus</t>
   </si>
   <si>
     <t>Dinamo Tbilisi</t>
   </si>
   <si>
-    <t>Vaprus</t>
-  </si>
-  <si>
-    <t>Paide</t>
+    <t>Pharco</t>
   </si>
   <si>
     <t>Haras El Hodood</t>
   </si>
   <si>
+    <t>National Bank of Egypt</t>
+  </si>
+  <si>
+    <t>Pyramids FC</t>
+  </si>
+  <si>
     <t>Rosenborg</t>
   </si>
   <si>
-    <t>Pyramids FC</t>
-  </si>
-  <si>
-    <t>National Bank of Egypt</t>
-  </si>
-  <si>
-    <t>Pharco</t>
-  </si>
-  <si>
     <t>Magesi</t>
   </si>
   <si>
     <t>Viking</t>
   </si>
   <si>
+    <t>Atlético Nacional</t>
+  </si>
+  <si>
     <t>Bahia</t>
   </si>
   <si>
-    <t>Atlético Nacional</t>
-  </si>
-  <si>
     <t>Hartford Athletic</t>
   </si>
   <si>
+    <t>FC Dallas</t>
+  </si>
+  <si>
+    <t>Montreal Impact</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>Orlando City</t>
+  </si>
+  <si>
+    <t>Houston Dynamo</t>
+  </si>
+  <si>
     <t>New England Revolution</t>
   </si>
   <si>
-    <t>Orlando City</t>
-  </si>
-  <si>
     <t>Philadelphia Union</t>
   </si>
   <si>
-    <t>FC Dallas</t>
-  </si>
-  <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
-    <t>Houston Dynamo</t>
-  </si>
-  <si>
-    <t>Montreal Impact</t>
-  </si>
-  <si>
     <t>Tulsa Roughnecks</t>
   </si>
   <si>
     <t>Portland Timbers II</t>
   </si>
   <si>
+    <t>Whitecaps II</t>
+  </si>
+  <si>
     <t>Nashville SC</t>
   </si>
   <si>
-    <t>Whitecaps II</t>
-  </si>
-  <si>
     <t>Nueva Chicago</t>
   </si>
   <si>
+    <t>Central Córdoba SdE</t>
+  </si>
+  <si>
+    <t>Cerro Porteño</t>
+  </si>
+  <si>
+    <t>San Diego</t>
+  </si>
+  <si>
     <t>Real Salt Lake</t>
   </si>
   <si>
-    <t>San Diego</t>
-  </si>
-  <si>
-    <t>Central Córdoba SdE</t>
-  </si>
-  <si>
-    <t>Cerro Porteño</t>
+    <t>Sporting Cristal</t>
   </si>
   <si>
     <t>Deportivo Táchira</t>
   </si>
   <si>
-    <t>Sporting Cristal</t>
-  </si>
-  <si>
     <t>SJ Earthquakes</t>
   </si>
   <si>
+    <t>Minnesota United</t>
+  </si>
+  <si>
     <t>Phoenix Rising</t>
   </si>
   <si>
-    <t>Minnesota United</t>
-  </si>
-  <si>
     <t>Colorado Rapids</t>
   </si>
   <si>
+    <t>complete</t>
+  </si>
+  <si>
     <t>incomplete</t>
+  </si>
+  <si>
+    <t>['10', '27', '60']</t>
   </si>
   <si>
     <t>[]</t>
@@ -1071,13 +1077,13 @@
         <v>125</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1086,13 +1092,13 @@
         <v>165</v>
       </c>
       <c r="L2">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M2">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="N2">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O2">
         <v>1.36</v>
@@ -1134,16 +1140,16 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AC2">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="AD2">
         <v>1.95</v>
       </c>
       <c r="AE2">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AF2">
         <v>0</v>
@@ -1158,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AK2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1173,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP2">
         <v>0</v>
@@ -1253,43 +1259,43 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L3">
-        <v>2.08</v>
+        <v>2.59</v>
       </c>
       <c r="M3">
-        <v>3.17</v>
+        <v>3.27</v>
       </c>
       <c r="N3">
-        <v>3.09</v>
+        <v>2.34</v>
       </c>
       <c r="O3">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="P3">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="Q3">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="R3">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S3">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T3">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U3">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V3">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="W3">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
         <v>1.06</v>
@@ -1298,82 +1304,82 @@
         <v>8.5</v>
       </c>
       <c r="Z3">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AA3">
         <v>3.1</v>
       </c>
       <c r="AB3">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AC3">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AD3">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="AE3">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF3">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI3">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AJ3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL3">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AM3">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AN3">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="AO3">
         <v>-1</v>
       </c>
       <c r="AP3">
+        <v>1.45</v>
+      </c>
+      <c r="AQ3">
+        <v>1.74</v>
+      </c>
+      <c r="AR3">
+        <v>2.18</v>
+      </c>
+      <c r="AS3">
+        <v>2.8</v>
+      </c>
+      <c r="AT3">
+        <v>3.7</v>
+      </c>
+      <c r="AU3">
+        <v>2.55</v>
+      </c>
+      <c r="AV3">
+        <v>1.97</v>
+      </c>
+      <c r="AW3">
         <v>1.58</v>
       </c>
-      <c r="AQ3">
-        <v>1.98</v>
-      </c>
-      <c r="AR3">
-        <v>2.55</v>
-      </c>
-      <c r="AS3">
-        <v>3.4</v>
-      </c>
-      <c r="AT3">
-        <v>4.6</v>
-      </c>
-      <c r="AU3">
-        <v>2.18</v>
-      </c>
-      <c r="AV3">
-        <v>1.73</v>
-      </c>
-      <c r="AW3">
-        <v>1.44</v>
-      </c>
       <c r="AX3">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AY3">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AZ3">
         <v>0</v>
@@ -1382,10 +1388,10 @@
         <v>0</v>
       </c>
       <c r="BB3">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="BC3">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="BD3" s="3">
         <v>45805.3125</v>
@@ -1399,7 +1405,7 @@
         <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
         <v>83</v>
@@ -1423,139 +1429,139 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L4">
-        <v>1.94</v>
+        <v>2.71</v>
       </c>
       <c r="M4">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
       <c r="N4">
-        <v>3.41</v>
+        <v>2.31</v>
       </c>
       <c r="O4">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="P4">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Q4">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="R4">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S4">
+        <v>2.62</v>
+      </c>
+      <c r="T4">
         <v>3</v>
       </c>
-      <c r="T4">
-        <v>2.75</v>
-      </c>
       <c r="U4">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>8.1</v>
       </c>
       <c r="W4">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X4">
         <v>1.06</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Z4">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AA4">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AB4">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AC4">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AD4">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="AE4">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF4">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH4">
-        <v>5.75</v>
+        <v>8</v>
       </c>
       <c r="AI4">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AJ4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL4">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AM4">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AN4">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AO4">
         <v>-1</v>
       </c>
       <c r="AP4">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="AQ4">
-        <v>1.42</v>
+        <v>1.74</v>
       </c>
       <c r="AR4">
-        <v>1.7</v>
+        <v>2.18</v>
       </c>
       <c r="AS4">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="AT4">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="AU4">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="AV4">
-        <v>2.55</v>
+        <v>1.97</v>
       </c>
       <c r="AW4">
+        <v>1.58</v>
+      </c>
+      <c r="AX4">
+        <v>1.36</v>
+      </c>
+      <c r="AY4">
+        <v>1.22</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>2.15</v>
+      </c>
+      <c r="BC4">
         <v>1.95</v>
-      </c>
-      <c r="AX4">
-        <v>1.6</v>
-      </c>
-      <c r="AY4">
-        <v>1.37</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>1.67</v>
-      </c>
-      <c r="BC4">
-        <v>2.4</v>
       </c>
       <c r="BD4" s="3">
         <v>45805.3125</v>
@@ -1593,25 +1599,25 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L5">
-        <v>2.71</v>
+        <v>2.08</v>
       </c>
       <c r="M5">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="N5">
-        <v>2.31</v>
+        <v>3.09</v>
       </c>
       <c r="O5">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="P5">
         <v>8.5</v>
       </c>
       <c r="Q5">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="R5">
         <v>1.42</v>
@@ -1644,10 +1650,10 @@
         <v>3.1</v>
       </c>
       <c r="AB5">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC5">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AD5">
         <v>3.85</v>
@@ -1668,52 +1674,52 @@
         <v>1.07</v>
       </c>
       <c r="AJ5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL5">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AM5">
         <v>1.25</v>
       </c>
       <c r="AN5">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AO5">
         <v>-1</v>
       </c>
       <c r="AP5">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ5">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="AR5">
+        <v>2.55</v>
+      </c>
+      <c r="AS5">
+        <v>3.4</v>
+      </c>
+      <c r="AT5">
+        <v>4.6</v>
+      </c>
+      <c r="AU5">
         <v>2.18</v>
       </c>
-      <c r="AS5">
-        <v>2.8</v>
-      </c>
-      <c r="AT5">
-        <v>3.8</v>
-      </c>
-      <c r="AU5">
-        <v>2.55</v>
-      </c>
       <c r="AV5">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="AW5">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AX5">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AY5">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AZ5">
         <v>0</v>
@@ -1722,10 +1728,10 @@
         <v>0</v>
       </c>
       <c r="BB5">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="BC5">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="BD5" s="3">
         <v>45805.3125</v>
@@ -1739,7 +1745,7 @@
         <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
         <v>83</v>
@@ -1763,55 +1769,55 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L6">
-        <v>2.59</v>
+        <v>1.94</v>
       </c>
       <c r="M6">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="N6">
-        <v>2.34</v>
+        <v>3.41</v>
       </c>
       <c r="O6">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="P6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="R6">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S6">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="T6">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U6">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V6">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
         <v>1.06</v>
       </c>
       <c r="Y6">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Z6">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AA6">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AB6">
         <v>1.89</v>
@@ -1820,70 +1826,70 @@
         <v>1.81</v>
       </c>
       <c r="AD6">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AE6">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AF6">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AH6">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="AI6">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AJ6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL6">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AM6">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AN6">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="AO6">
         <v>-1</v>
       </c>
       <c r="AP6">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="AQ6">
-        <v>1.74</v>
+        <v>1.42</v>
       </c>
       <c r="AR6">
-        <v>2.18</v>
+        <v>1.7</v>
       </c>
       <c r="AS6">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AT6">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="AU6">
+        <v>3.4</v>
+      </c>
+      <c r="AV6">
         <v>2.55</v>
       </c>
-      <c r="AV6">
-        <v>1.97</v>
-      </c>
       <c r="AW6">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AX6">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AY6">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="AZ6">
         <v>0</v>
@@ -1892,10 +1898,10 @@
         <v>0</v>
       </c>
       <c r="BB6">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="BC6">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="BD6" s="3">
         <v>45805.3125</v>
@@ -1933,94 +1939,94 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L7">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="M7">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="N7">
-        <v>3.45</v>
+        <v>2.96</v>
       </c>
       <c r="O7">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="P7">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="Q7">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="R7">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="S7">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="T7">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="U7">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="V7">
-        <v>7.3</v>
+        <v>5.75</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="Z7">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AA7">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AB7">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AC7">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AD7">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AE7">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AF7">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="AG7">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AH7">
-        <v>6.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI7">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AJ7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL7">
         <v>1.27</v>
       </c>
       <c r="AM7">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AN7">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AO7">
         <v>-1</v>
@@ -2062,10 +2068,10 @@
         <v>0</v>
       </c>
       <c r="BB7">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="BC7">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="BD7" s="3">
         <v>45805.54166666666</v>
@@ -2079,7 +2085,7 @@
         <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
         <v>83</v>
@@ -2103,16 +2109,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L8">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="M8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N8">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O8">
         <v>1.17</v>
@@ -2124,73 +2130,73 @@
         <v>5</v>
       </c>
       <c r="R8">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S8">
         <v>3.4</v>
       </c>
       <c r="T8">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="U8">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="V8">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="W8">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X8">
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z8">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AA8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AB8">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="AC8">
-        <v>2.69</v>
+        <v>2.27</v>
       </c>
       <c r="AD8">
-        <v>1.89</v>
+        <v>2.41</v>
       </c>
       <c r="AE8">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="AF8">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG8">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AH8">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="AI8">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AJ8" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK8" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL8">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AM8">
         <v>1.06</v>
       </c>
       <c r="AN8">
-        <v>4.2</v>
+        <v>3.99</v>
       </c>
       <c r="AO8">
         <v>-1</v>
@@ -2273,94 +2279,94 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L9">
-        <v>2.44</v>
+        <v>1.96</v>
       </c>
       <c r="M9">
-        <v>3.51</v>
+        <v>3.35</v>
       </c>
       <c r="N9">
-        <v>2.35</v>
+        <v>3.45</v>
       </c>
       <c r="O9">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="P9">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="R9">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="S9">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="T9">
-        <v>2.36</v>
+        <v>2.85</v>
       </c>
       <c r="U9">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="V9">
-        <v>5.45</v>
+        <v>7.3</v>
       </c>
       <c r="W9">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>15</v>
+        <v>8.5</v>
       </c>
       <c r="Z9">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AA9">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="AB9">
-        <v>1.52</v>
+        <v>2.05</v>
       </c>
       <c r="AC9">
-        <v>2.37</v>
+        <v>1.65</v>
       </c>
       <c r="AD9">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="AE9">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AF9">
-        <v>1.5</v>
+        <v>1.84</v>
       </c>
       <c r="AG9">
-        <v>2.45</v>
+        <v>1.92</v>
       </c>
       <c r="AH9">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="AI9">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AJ9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL9">
         <v>1.27</v>
       </c>
       <c r="AM9">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AN9">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AO9">
         <v>-1</v>
@@ -2402,10 +2408,10 @@
         <v>0</v>
       </c>
       <c r="BB9">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="BC9">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="BD9" s="3">
         <v>45805.54166666666</v>
@@ -2443,127 +2449,127 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L10">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="M10">
-        <v>3.34</v>
+        <v>5.1</v>
       </c>
       <c r="N10">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="O10">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="P10">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Q10">
-        <v>3.1</v>
+        <v>5.15</v>
       </c>
       <c r="R10">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="S10">
-        <v>2.4</v>
+        <v>3.28</v>
       </c>
       <c r="T10">
-        <v>3.3</v>
+        <v>2.46</v>
       </c>
       <c r="U10">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="V10">
-        <v>8.5</v>
+        <v>5.6</v>
       </c>
       <c r="W10">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>7.8</v>
+        <v>12.4</v>
       </c>
       <c r="Z10">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AA10">
-        <v>2.8</v>
+        <v>4.25</v>
       </c>
       <c r="AB10">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AC10">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AD10">
-        <v>4.4</v>
+        <v>2.55</v>
       </c>
       <c r="AE10">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="AF10">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="AG10">
         <v>1.55</v>
       </c>
       <c r="AH10">
-        <v>9</v>
+        <v>4.9</v>
       </c>
       <c r="AI10">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AJ10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL10">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AM10">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AN10">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="AO10">
         <v>-1</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ10">
         <v>0</v>
@@ -2572,10 +2578,10 @@
         <v>0</v>
       </c>
       <c r="BB10">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="BC10">
-        <v>3.1</v>
+        <v>5.15</v>
       </c>
       <c r="BD10" s="3">
         <v>45805.58333333334</v>
@@ -2589,10 +2595,10 @@
         <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
         <v>94</v>
@@ -2613,139 +2619,139 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L11">
-        <v>2.72</v>
+        <v>1.6</v>
       </c>
       <c r="M11">
-        <v>3.26</v>
+        <v>3.34</v>
       </c>
       <c r="N11">
-        <v>2.25</v>
+        <v>5.2</v>
       </c>
       <c r="O11">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="P11">
-        <v>8.25</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="R11">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S11">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="T11">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U11">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="Z11">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AA11">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="AB11">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AC11">
-        <v>1.84</v>
+        <v>1.57</v>
       </c>
       <c r="AD11">
-        <v>3.55</v>
+        <v>4.35</v>
       </c>
       <c r="AE11">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AF11">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AG11">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AH11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI11">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AJ11" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK11" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL11">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AM11">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AN11">
-        <v>1.35</v>
+        <v>2</v>
       </c>
       <c r="AO11">
         <v>-1</v>
       </c>
       <c r="AP11">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="AQ11">
-        <v>1.41</v>
+        <v>1.76</v>
       </c>
       <c r="AR11">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="AS11">
-        <v>2.19</v>
+        <v>2.88</v>
       </c>
       <c r="AT11">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="AU11">
-        <v>3.58</v>
+        <v>2.5</v>
       </c>
       <c r="AV11">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="AW11">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AX11">
+        <v>1.36</v>
+      </c>
+      <c r="AY11">
+        <v>1.22</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
         <v>1.57</v>
       </c>
-      <c r="AY11">
-        <v>1.32</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>2.3</v>
-      </c>
       <c r="BC11">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="BD11" s="3">
         <v>45805.58333333334</v>
@@ -2783,127 +2789,127 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L12">
-        <v>3.94</v>
+        <v>3.45</v>
       </c>
       <c r="M12">
-        <v>3.27</v>
+        <v>2.68</v>
       </c>
       <c r="N12">
-        <v>1.78</v>
+        <v>2.19</v>
       </c>
       <c r="O12">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="P12">
-        <v>9.25</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="R12">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S12">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="T12">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U12">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z12">
+        <v>1.31</v>
+      </c>
+      <c r="AA12">
+        <v>3.23</v>
+      </c>
+      <c r="AB12">
+        <v>1.95</v>
+      </c>
+      <c r="AC12">
+        <v>1.75</v>
+      </c>
+      <c r="AD12">
+        <v>3.34</v>
+      </c>
+      <c r="AE12">
         <v>1.29</v>
       </c>
-      <c r="AA12">
-        <v>3.5</v>
-      </c>
-      <c r="AB12">
-        <v>1.91</v>
-      </c>
-      <c r="AC12">
-        <v>1.79</v>
-      </c>
-      <c r="AD12">
-        <v>3.2</v>
-      </c>
-      <c r="AE12">
-        <v>1.3</v>
-      </c>
       <c r="AF12">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG12">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH12">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AI12">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AJ12" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK12" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL12">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AM12">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AN12">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AO12">
         <v>-1</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ12">
         <v>0</v>
@@ -2912,10 +2918,10 @@
         <v>0</v>
       </c>
       <c r="BB12">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="BC12">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="BD12" s="3">
         <v>45805.58333333334</v>
@@ -2953,127 +2959,127 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L13">
-        <v>3.45</v>
+        <v>3.94</v>
       </c>
       <c r="M13">
-        <v>2.68</v>
+        <v>3.27</v>
       </c>
       <c r="N13">
-        <v>2.19</v>
+        <v>1.78</v>
       </c>
       <c r="O13">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="P13">
-        <v>7</v>
+        <v>9.25</v>
       </c>
       <c r="Q13">
+        <v>1.57</v>
+      </c>
+      <c r="R13">
+        <v>1.38</v>
+      </c>
+      <c r="S13">
+        <v>2.9</v>
+      </c>
+      <c r="T13">
+        <v>2.76</v>
+      </c>
+      <c r="U13">
+        <v>1.42</v>
+      </c>
+      <c r="V13">
+        <v>6.4</v>
+      </c>
+      <c r="W13">
+        <v>1.09</v>
+      </c>
+      <c r="X13">
+        <v>1.02</v>
+      </c>
+      <c r="Y13">
+        <v>8.6</v>
+      </c>
+      <c r="Z13">
+        <v>1.26</v>
+      </c>
+      <c r="AA13">
+        <v>3.5</v>
+      </c>
+      <c r="AB13">
+        <v>1.91</v>
+      </c>
+      <c r="AC13">
+        <v>1.79</v>
+      </c>
+      <c r="AD13">
+        <v>3.25</v>
+      </c>
+      <c r="AE13">
+        <v>1.3</v>
+      </c>
+      <c r="AF13">
+        <v>1.8</v>
+      </c>
+      <c r="AG13">
         <v>1.85</v>
       </c>
-      <c r="R13">
-        <v>1.42</v>
-      </c>
-      <c r="S13">
-        <v>2.47</v>
-      </c>
-      <c r="T13">
-        <v>3</v>
-      </c>
-      <c r="U13">
-        <v>1.33</v>
-      </c>
-      <c r="V13">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W13">
-        <v>1.06</v>
-      </c>
-      <c r="X13">
-        <v>1.03</v>
-      </c>
-      <c r="Y13">
-        <v>7.6</v>
-      </c>
-      <c r="Z13">
-        <v>1.33</v>
-      </c>
-      <c r="AA13">
-        <v>3</v>
-      </c>
-      <c r="AB13">
-        <v>2.05</v>
-      </c>
-      <c r="AC13">
-        <v>1.61</v>
-      </c>
-      <c r="AD13">
-        <v>3.6</v>
-      </c>
-      <c r="AE13">
-        <v>1.2</v>
-      </c>
-      <c r="AF13">
-        <v>1.75</v>
-      </c>
-      <c r="AG13">
-        <v>1.9</v>
-      </c>
       <c r="AH13">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="AI13">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AJ13" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK13" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL13">
-        <v>1.35</v>
+        <v>2</v>
       </c>
       <c r="AM13">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AN13">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AO13">
         <v>-1</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ13">
         <v>0</v>
@@ -3082,10 +3088,10 @@
         <v>0</v>
       </c>
       <c r="BB13">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="BC13">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="BD13" s="3">
         <v>45805.58333333334</v>
@@ -3099,10 +3105,10 @@
         <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
         <v>97</v>
@@ -3123,127 +3129,127 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L14">
-        <v>1.2</v>
+        <v>2.72</v>
       </c>
       <c r="M14">
-        <v>5.1</v>
+        <v>3.26</v>
       </c>
       <c r="N14">
-        <v>11</v>
+        <v>2.25</v>
       </c>
       <c r="O14">
-        <v>1.17</v>
+        <v>2.3</v>
       </c>
       <c r="P14">
-        <v>15</v>
+        <v>8.25</v>
       </c>
       <c r="Q14">
-        <v>5.15</v>
+        <v>1.73</v>
       </c>
       <c r="R14">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="S14">
-        <v>3.28</v>
+        <v>2.63</v>
       </c>
       <c r="T14">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="U14">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="V14">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="Z14">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AA14">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="AB14">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AC14">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AD14">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="AE14">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AF14">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AG14">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="AH14">
-        <v>5.05</v>
+        <v>7</v>
       </c>
       <c r="AI14">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AJ14" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK14" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL14">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="AM14">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="AN14">
-        <v>4.45</v>
+        <v>1.35</v>
       </c>
       <c r="AO14">
         <v>-1</v>
       </c>
       <c r="AP14">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AQ14">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AR14">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="AS14">
-        <v>2.55</v>
+        <v>2.19</v>
       </c>
       <c r="AT14">
-        <v>3.32</v>
+        <v>2.88</v>
       </c>
       <c r="AU14">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="AV14">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AW14">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AX14">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AY14">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AZ14">
         <v>0</v>
@@ -3252,10 +3258,10 @@
         <v>0</v>
       </c>
       <c r="BB14">
-        <v>1.17</v>
+        <v>2.3</v>
       </c>
       <c r="BC14">
-        <v>5.15</v>
+        <v>1.73</v>
       </c>
       <c r="BD14" s="3">
         <v>45805.58333333334</v>
@@ -3293,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L15">
         <v>1.32</v>
@@ -3368,10 +3374,10 @@
         <v>1.07</v>
       </c>
       <c r="AJ15" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK15" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL15">
         <v>1.06</v>
@@ -3463,7 +3469,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L16">
         <v>1.27</v>
@@ -3538,10 +3544,10 @@
         <v>1.33</v>
       </c>
       <c r="AJ16" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK16" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL16">
         <v>1.17</v>
@@ -3633,37 +3639,37 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L17">
-        <v>1.81</v>
+        <v>2.29</v>
       </c>
       <c r="M17">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="N17">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="O17">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="P17">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="Q17">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="R17">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S17">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T17">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U17">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V17">
         <v>9</v>
@@ -3681,7 +3687,7 @@
         <v>1.38</v>
       </c>
       <c r="AA17">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AB17">
         <v>2.05</v>
@@ -3690,10 +3696,10 @@
         <v>1.61</v>
       </c>
       <c r="AD17">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AE17">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF17">
         <v>1.95</v>
@@ -3702,58 +3708,58 @@
         <v>1.8</v>
       </c>
       <c r="AH17">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AI17">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AJ17" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK17" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL17">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AM17">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AN17">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="AO17">
         <v>-1</v>
       </c>
       <c r="AP17">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AQ17">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AR17">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AS17">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AT17">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AU17">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="AV17">
-        <v>2.17</v>
+        <v>2.45</v>
       </c>
       <c r="AW17">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AX17">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AY17">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AZ17">
         <v>0</v>
@@ -3762,10 +3768,10 @@
         <v>0</v>
       </c>
       <c r="BB17">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="BC17">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="BD17" s="3">
         <v>45805.79166666666</v>
@@ -3803,37 +3809,37 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L18">
-        <v>2.29</v>
+        <v>1.81</v>
       </c>
       <c r="M18">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="N18">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="O18">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="R18">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S18">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T18">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U18">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V18">
         <v>9</v>
@@ -3842,16 +3848,16 @@
         <v>1.07</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB18">
         <v>2.05</v>
@@ -3860,10 +3866,10 @@
         <v>1.61</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF18">
         <v>1.95</v>
@@ -3872,58 +3878,58 @@
         <v>1.8</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ18" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK18" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO18">
         <v>-1</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ18">
         <v>0</v>
@@ -3932,10 +3938,10 @@
         <v>0</v>
       </c>
       <c r="BB18">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="BC18">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="BD18" s="3">
         <v>45805.79166666666</v>
@@ -3973,16 +3979,16 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L19">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="M19">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="N19">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="O19">
         <v>1.53</v>
@@ -3994,34 +4000,34 @@
         <v>2.6</v>
       </c>
       <c r="R19">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S19">
         <v>3.2</v>
       </c>
       <c r="T19">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="U19">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V19">
-        <v>5.8</v>
+        <v>5.35</v>
       </c>
       <c r="W19">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z19">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AA19">
-        <v>3.84</v>
+        <v>4.15</v>
       </c>
       <c r="AB19">
         <v>1.73</v>
@@ -4036,31 +4042,31 @@
         <v>1.36</v>
       </c>
       <c r="AF19">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG19">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH19">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="AI19">
+        <v>1.16</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>168</v>
+      </c>
+      <c r="AL19">
         <v>1.15</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK19" t="s">
-        <v>166</v>
-      </c>
-      <c r="AL19">
-        <v>1.22</v>
       </c>
       <c r="AM19">
         <v>1.22</v>
       </c>
       <c r="AN19">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="AO19">
         <v>-1</v>
@@ -4069,31 +4075,31 @@
         <v>0</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU19">
         <v>0</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ19">
         <v>0</v>
@@ -4143,31 +4149,31 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L20">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="M20">
-        <v>3.45</v>
+        <v>3.91</v>
       </c>
       <c r="N20">
-        <v>3.29</v>
+        <v>5.1</v>
       </c>
       <c r="O20">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="P20">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Q20">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="R20">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S20">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T20">
         <v>2.5</v>
@@ -4176,10 +4182,10 @@
         <v>1.5</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W20">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
         <v>1.04</v>
@@ -4188,82 +4194,82 @@
         <v>10</v>
       </c>
       <c r="Z20">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AA20">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AB20">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AC20">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AD20">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AE20">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AF20">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG20">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH20">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="AI20">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AJ20" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK20" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL20">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AM20">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AN20">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AO20">
         <v>-1</v>
       </c>
       <c r="AP20">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AQ20">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AR20">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AS20">
+        <v>2.4</v>
+      </c>
+      <c r="AT20">
+        <v>3.1</v>
+      </c>
+      <c r="AU20">
+        <v>3.05</v>
+      </c>
+      <c r="AV20">
         <v>2.25</v>
       </c>
-      <c r="AT20">
-        <v>2.9</v>
-      </c>
-      <c r="AU20">
-        <v>3.2</v>
-      </c>
-      <c r="AV20">
-        <v>2.38</v>
-      </c>
       <c r="AW20">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AX20">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AY20">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AZ20">
         <v>0</v>
@@ -4272,10 +4278,10 @@
         <v>0</v>
       </c>
       <c r="BB20">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="BC20">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="BD20" s="3">
         <v>45805.85416666666</v>
@@ -4313,127 +4319,127 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L21">
-        <v>2.39</v>
+        <v>1.44</v>
       </c>
       <c r="M21">
-        <v>3.34</v>
+        <v>4.5</v>
       </c>
       <c r="N21">
-        <v>2.49</v>
+        <v>4.9</v>
       </c>
       <c r="O21">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="P21">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q21">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="R21">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="S21">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T21">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="U21">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="V21">
+        <v>4.5</v>
+      </c>
+      <c r="W21">
+        <v>1.18</v>
+      </c>
+      <c r="X21">
+        <v>1.01</v>
+      </c>
+      <c r="Y21">
+        <v>17</v>
+      </c>
+      <c r="Z21">
+        <v>1.14</v>
+      </c>
+      <c r="AA21">
         <v>5.5</v>
       </c>
-      <c r="W21">
-        <v>1.14</v>
-      </c>
-      <c r="X21">
-        <v>1.04</v>
-      </c>
-      <c r="Y21">
-        <v>10</v>
-      </c>
-      <c r="Z21">
-        <v>1.2</v>
-      </c>
-      <c r="AA21">
-        <v>4.33</v>
-      </c>
       <c r="AB21">
+        <v>1.45</v>
+      </c>
+      <c r="AC21">
+        <v>2.63</v>
+      </c>
+      <c r="AD21">
+        <v>2.15</v>
+      </c>
+      <c r="AE21">
         <v>1.61</v>
       </c>
-      <c r="AC21">
-        <v>2.2</v>
-      </c>
-      <c r="AD21">
-        <v>2.55</v>
-      </c>
-      <c r="AE21">
-        <v>1.5</v>
-      </c>
       <c r="AF21">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AG21">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AH21">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="AI21">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AJ21" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK21" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL21">
-        <v>1.47</v>
+        <v>1.12</v>
       </c>
       <c r="AM21">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AN21">
-        <v>1.52</v>
+        <v>2.65</v>
       </c>
       <c r="AO21">
         <v>-1</v>
       </c>
       <c r="AP21">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AQ21">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AR21">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AS21">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="AT21">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="AU21">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AV21">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="AW21">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AX21">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AY21">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AZ21">
         <v>0</v>
@@ -4442,10 +4448,10 @@
         <v>0</v>
       </c>
       <c r="BB21">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="BC21">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="BD21" s="3">
         <v>45805.85416666666</v>
@@ -4483,31 +4489,31 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L22">
-        <v>2.91</v>
+        <v>1.8</v>
       </c>
       <c r="M22">
-        <v>3.21</v>
+        <v>3.38</v>
       </c>
       <c r="N22">
-        <v>2.15</v>
+        <v>3.71</v>
       </c>
       <c r="O22">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="P22">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Q22">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="R22">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S22">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T22">
         <v>2.63</v>
@@ -4516,10 +4522,10 @@
         <v>1.44</v>
       </c>
       <c r="V22">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W22">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X22">
         <v>1.05</v>
@@ -4528,82 +4534,82 @@
         <v>9.5</v>
       </c>
       <c r="Z22">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AA22">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AB22">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AC22">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AD22">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AE22">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AF22">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG22">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH22">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AI22">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AJ22" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK22" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL22">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="AM22">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AN22">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="AO22">
         <v>-1</v>
       </c>
       <c r="AP22">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AQ22">
+        <v>1.57</v>
+      </c>
+      <c r="AR22">
+        <v>1.92</v>
+      </c>
+      <c r="AS22">
+        <v>2.43</v>
+      </c>
+      <c r="AT22">
+        <v>3.15</v>
+      </c>
+      <c r="AU22">
+        <v>2.95</v>
+      </c>
+      <c r="AV22">
+        <v>2.23</v>
+      </c>
+      <c r="AW22">
+        <v>1.77</v>
+      </c>
+      <c r="AX22">
         <v>1.47</v>
       </c>
-      <c r="AR22">
-        <v>1.76</v>
-      </c>
-      <c r="AS22">
-        <v>2.17</v>
-      </c>
-      <c r="AT22">
-        <v>2.75</v>
-      </c>
-      <c r="AU22">
-        <v>3.4</v>
-      </c>
-      <c r="AV22">
-        <v>2.48</v>
-      </c>
-      <c r="AW22">
-        <v>1.94</v>
-      </c>
-      <c r="AX22">
-        <v>1.6</v>
-      </c>
       <c r="AY22">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AZ22">
         <v>0</v>
@@ -4612,10 +4618,10 @@
         <v>0</v>
       </c>
       <c r="BB22">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="BC22">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="BD22" s="3">
         <v>45805.85416666666</v>
@@ -4653,43 +4659,43 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L23">
-        <v>1.5</v>
+        <v>2.39</v>
       </c>
       <c r="M23">
-        <v>3.91</v>
+        <v>3.34</v>
       </c>
       <c r="N23">
-        <v>5.1</v>
+        <v>2.49</v>
       </c>
       <c r="O23">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="P23">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R23">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S23">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T23">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U23">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V23">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W23">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X23">
         <v>1.04</v>
@@ -4698,82 +4704,82 @@
         <v>10</v>
       </c>
       <c r="Z23">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AA23">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AB23">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC23">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD23">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AE23">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AF23">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AG23">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AH23">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="AI23">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AJ23" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK23" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL23">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="AM23">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AN23">
-        <v>2.2</v>
+        <v>1.52</v>
       </c>
       <c r="AO23">
         <v>-1</v>
       </c>
       <c r="AP23">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AQ23">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR23">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AS23">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="AT23">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AU23">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AV23">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="AW23">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AX23">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AY23">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AZ23">
         <v>0</v>
@@ -4782,10 +4788,10 @@
         <v>0</v>
       </c>
       <c r="BB23">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="BC23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD23" s="3">
         <v>45805.85416666666</v>
@@ -4823,16 +4829,16 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L24">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="M24">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="N24">
-        <v>3.71</v>
+        <v>3.57</v>
       </c>
       <c r="O24">
         <v>1.57</v>
@@ -4841,7 +4847,7 @@
         <v>9.5</v>
       </c>
       <c r="Q24">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R24">
         <v>1.36</v>
@@ -4865,25 +4871,25 @@
         <v>1.05</v>
       </c>
       <c r="Y24">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="Z24">
         <v>1.28</v>
       </c>
       <c r="AA24">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AB24">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC24">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AD24">
         <v>3.1</v>
       </c>
       <c r="AE24">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AF24">
         <v>1.75</v>
@@ -4898,52 +4904,52 @@
         <v>1.12</v>
       </c>
       <c r="AJ24" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK24" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL24">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AM24">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AN24">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AO24">
         <v>-1</v>
       </c>
       <c r="AP24">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AQ24">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AR24">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AS24">
-        <v>2.43</v>
+        <v>2.08</v>
       </c>
       <c r="AT24">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="AU24">
-        <v>2.95</v>
+        <v>3.55</v>
       </c>
       <c r="AV24">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="AW24">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AX24">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AY24">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AZ24">
         <v>0</v>
@@ -4955,7 +4961,7 @@
         <v>1.57</v>
       </c>
       <c r="BC24">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="BD24" s="3">
         <v>45805.85416666666</v>
@@ -4993,127 +4999,127 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L25">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="M25">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N25">
-        <v>3.57</v>
+        <v>3.29</v>
       </c>
       <c r="O25">
+        <v>1.67</v>
+      </c>
+      <c r="P25">
+        <v>11.5</v>
+      </c>
+      <c r="Q25">
+        <v>2.25</v>
+      </c>
+      <c r="R25">
+        <v>1.3</v>
+      </c>
+      <c r="S25">
+        <v>3.4</v>
+      </c>
+      <c r="T25">
+        <v>2.5</v>
+      </c>
+      <c r="U25">
+        <v>1.5</v>
+      </c>
+      <c r="V25">
+        <v>6</v>
+      </c>
+      <c r="W25">
+        <v>1.13</v>
+      </c>
+      <c r="X25">
+        <v>1.04</v>
+      </c>
+      <c r="Y25">
+        <v>10</v>
+      </c>
+      <c r="Z25">
+        <v>1.2</v>
+      </c>
+      <c r="AA25">
+        <v>4.33</v>
+      </c>
+      <c r="AB25">
+        <v>1.76</v>
+      </c>
+      <c r="AC25">
+        <v>1.94</v>
+      </c>
+      <c r="AD25">
+        <v>2.55</v>
+      </c>
+      <c r="AE25">
+        <v>1.5</v>
+      </c>
+      <c r="AF25">
         <v>1.57</v>
       </c>
-      <c r="P25">
-        <v>9.5</v>
-      </c>
-      <c r="Q25">
-        <v>2.5</v>
-      </c>
-      <c r="R25">
-        <v>1.36</v>
-      </c>
-      <c r="S25">
-        <v>3</v>
-      </c>
-      <c r="T25">
-        <v>2.63</v>
-      </c>
-      <c r="U25">
-        <v>1.44</v>
-      </c>
-      <c r="V25">
-        <v>7</v>
-      </c>
-      <c r="W25">
-        <v>1.1</v>
-      </c>
-      <c r="X25">
-        <v>1.05</v>
-      </c>
-      <c r="Y25">
-        <v>9</v>
-      </c>
-      <c r="Z25">
+      <c r="AG25">
+        <v>2.25</v>
+      </c>
+      <c r="AH25">
+        <v>4.5</v>
+      </c>
+      <c r="AI25">
+        <v>1.2</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK25" t="s">
+        <v>168</v>
+      </c>
+      <c r="AL25">
+        <v>1.38</v>
+      </c>
+      <c r="AM25">
         <v>1.28</v>
       </c>
-      <c r="AA25">
-        <v>3.55</v>
-      </c>
-      <c r="AB25">
-        <v>1.8</v>
-      </c>
-      <c r="AC25">
-        <v>1.9</v>
-      </c>
-      <c r="AD25">
-        <v>3.1</v>
-      </c>
-      <c r="AE25">
-        <v>1.36</v>
-      </c>
-      <c r="AF25">
-        <v>1.75</v>
-      </c>
-      <c r="AG25">
-        <v>2</v>
-      </c>
-      <c r="AH25">
-        <v>5.75</v>
-      </c>
-      <c r="AI25">
-        <v>1.12</v>
-      </c>
-      <c r="AJ25" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK25" t="s">
-        <v>166</v>
-      </c>
-      <c r="AL25">
-        <v>1.26</v>
-      </c>
-      <c r="AM25">
-        <v>1.29</v>
-      </c>
       <c r="AN25">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AO25">
         <v>-1</v>
       </c>
       <c r="AP25">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AQ25">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR25">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AS25">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AT25">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="AU25">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="AV25">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AW25">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AX25">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AY25">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AZ25">
         <v>0</v>
@@ -5122,10 +5128,10 @@
         <v>0</v>
       </c>
       <c r="BB25">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="BC25">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="BD25" s="3">
         <v>45805.85416666666</v>
@@ -5163,127 +5169,127 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L26">
+        <v>2.91</v>
+      </c>
+      <c r="M26">
+        <v>3.21</v>
+      </c>
+      <c r="N26">
+        <v>2.15</v>
+      </c>
+      <c r="O26">
+        <v>2.1</v>
+      </c>
+      <c r="P26">
+        <v>10</v>
+      </c>
+      <c r="Q26">
+        <v>1.8</v>
+      </c>
+      <c r="R26">
+        <v>1.33</v>
+      </c>
+      <c r="S26">
+        <v>3.25</v>
+      </c>
+      <c r="T26">
+        <v>2.63</v>
+      </c>
+      <c r="U26">
         <v>1.44</v>
       </c>
-      <c r="M26">
-        <v>4.5</v>
-      </c>
-      <c r="N26">
-        <v>4.9</v>
-      </c>
-      <c r="O26">
-        <v>1.3</v>
-      </c>
-      <c r="P26">
-        <v>15</v>
-      </c>
-      <c r="Q26">
-        <v>3.4</v>
-      </c>
-      <c r="R26">
-        <v>1.22</v>
-      </c>
-      <c r="S26">
-        <v>4</v>
-      </c>
-      <c r="T26">
-        <v>2.1</v>
-      </c>
-      <c r="U26">
-        <v>1.67</v>
-      </c>
       <c r="V26">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="W26">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="Z26">
+        <v>1.25</v>
+      </c>
+      <c r="AA26">
+        <v>3.75</v>
+      </c>
+      <c r="AB26">
+        <v>1.83</v>
+      </c>
+      <c r="AC26">
+        <v>1.87</v>
+      </c>
+      <c r="AD26">
+        <v>3</v>
+      </c>
+      <c r="AE26">
+        <v>1.38</v>
+      </c>
+      <c r="AF26">
+        <v>1.62</v>
+      </c>
+      <c r="AG26">
+        <v>2.2</v>
+      </c>
+      <c r="AH26">
+        <v>5.5</v>
+      </c>
+      <c r="AI26">
         <v>1.14</v>
       </c>
-      <c r="AA26">
-        <v>5.5</v>
-      </c>
-      <c r="AB26">
-        <v>1.45</v>
-      </c>
-      <c r="AC26">
-        <v>2.63</v>
-      </c>
-      <c r="AD26">
-        <v>2.15</v>
-      </c>
-      <c r="AE26">
-        <v>1.61</v>
-      </c>
-      <c r="AF26">
-        <v>1.67</v>
-      </c>
-      <c r="AG26">
-        <v>2.1</v>
-      </c>
-      <c r="AH26">
-        <v>3.7</v>
-      </c>
-      <c r="AI26">
-        <v>1.25</v>
-      </c>
       <c r="AJ26" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK26" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL26">
-        <v>1.12</v>
+        <v>1.55</v>
       </c>
       <c r="AM26">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AN26">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="AO26">
         <v>-1</v>
       </c>
       <c r="AP26">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AQ26">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AR26">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AS26">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="AT26">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AU26">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="AV26">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="AW26">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AX26">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AY26">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AZ26">
         <v>0</v>
@@ -5292,10 +5298,10 @@
         <v>0</v>
       </c>
       <c r="BB26">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="BC26">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="BD26" s="3">
         <v>45805.85416666666</v>
@@ -5333,16 +5339,16 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L27">
-        <v>1.99</v>
+        <v>2.13</v>
       </c>
       <c r="M27">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="N27">
-        <v>3.3</v>
+        <v>3.03</v>
       </c>
       <c r="O27">
         <v>1.67</v>
@@ -5354,40 +5360,40 @@
         <v>2.5</v>
       </c>
       <c r="R27">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S27">
         <v>2.75</v>
       </c>
       <c r="T27">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="U27">
         <v>1.37</v>
       </c>
       <c r="V27">
-        <v>6.75</v>
+        <v>6.7</v>
       </c>
       <c r="W27">
         <v>1.08</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z27">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AA27">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="AB27">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC27">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AD27">
         <v>3.3</v>
@@ -5396,22 +5402,22 @@
         <v>1.27</v>
       </c>
       <c r="AF27">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG27">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AH27">
-        <v>6.4</v>
+        <v>6.35</v>
       </c>
       <c r="AI27">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AJ27" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK27" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL27">
         <v>1.3</v>
@@ -5420,40 +5426,40 @@
         <v>0</v>
       </c>
       <c r="AN27">
-        <v>1.56</v>
+        <v>1.74</v>
       </c>
       <c r="AO27">
         <v>-1</v>
       </c>
       <c r="AP27">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU27">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV27">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW27">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX27">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY27">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ27">
         <v>0</v>
@@ -5503,43 +5509,43 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P28">
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X28">
         <v>0</v>
@@ -5548,49 +5554,49 @@
         <v>0</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ28" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK28" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AM28">
         <v>0</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AO28">
         <v>-1</v>
@@ -5632,10 +5638,10 @@
         <v>0</v>
       </c>
       <c r="BB28">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC28">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BD28" s="3">
         <v>45805.875</v>
@@ -5649,7 +5655,7 @@
         <v>65</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s">
         <v>83</v>
@@ -5673,127 +5679,127 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L29">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="M29">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="N29">
-        <v>3.83</v>
+        <v>5.2</v>
       </c>
       <c r="O29">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="P29">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="R29">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
         <v>1.44</v>
       </c>
-      <c r="V29">
-        <v>7</v>
-      </c>
-      <c r="W29">
-        <v>1.1</v>
-      </c>
-      <c r="X29">
-        <v>1.05</v>
-      </c>
-      <c r="Y29">
-        <v>9.5</v>
-      </c>
-      <c r="Z29">
-        <v>1.28</v>
-      </c>
-      <c r="AA29">
-        <v>3.65</v>
-      </c>
-      <c r="AB29">
-        <v>1.83</v>
-      </c>
       <c r="AC29">
-        <v>1.87</v>
+        <v>2.62</v>
       </c>
       <c r="AD29">
-        <v>3.1</v>
+        <v>1.96</v>
       </c>
       <c r="AE29">
-        <v>1.35</v>
+        <v>1.79</v>
       </c>
       <c r="AF29">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH29">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AI29">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK29" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL29">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AM29">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN29">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO29">
         <v>-1</v>
       </c>
       <c r="AP29">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ29">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR29">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS29">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AT29">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU29">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AV29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW29">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX29">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY29">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ29">
         <v>0</v>
@@ -5802,10 +5808,10 @@
         <v>0</v>
       </c>
       <c r="BB29">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="BC29">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="BD29" s="3">
         <v>45805.875</v>
@@ -5819,7 +5825,7 @@
         <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s">
         <v>83</v>
@@ -5843,127 +5849,127 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ30" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK30" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL30">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AM30">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO30">
         <v>-1</v>
       </c>
       <c r="AP30">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU30">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AV30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW30">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX30">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY30">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ30">
         <v>0</v>
@@ -5972,10 +5978,10 @@
         <v>0</v>
       </c>
       <c r="BB30">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BC30">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BD30" s="3">
         <v>45805.875</v>
@@ -6013,7 +6019,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L31">
         <v>2.17</v>
@@ -6034,28 +6040,28 @@
         <v>2.4</v>
       </c>
       <c r="R31">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="S31">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="T31">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="U31">
         <v>1.2</v>
       </c>
       <c r="V31">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="W31">
         <v>1.02</v>
       </c>
       <c r="X31">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y31">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="Z31">
         <v>1.6</v>
@@ -6064,34 +6070,34 @@
         <v>2.1</v>
       </c>
       <c r="AB31">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AC31">
         <v>1.34</v>
       </c>
       <c r="AD31">
-        <v>6.22</v>
+        <v>6.24</v>
       </c>
       <c r="AE31">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF31">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AG31">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AH31">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI31">
         <v>1.03</v>
       </c>
       <c r="AJ31" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK31" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL31">
         <v>1.44</v>
@@ -6109,19 +6115,19 @@
         <v>1.38</v>
       </c>
       <c r="AQ31">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AR31">
         <v>2.17</v>
       </c>
       <c r="AS31">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="AT31">
-        <v>3.92</v>
+        <v>4.35</v>
       </c>
       <c r="AU31">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AV31">
         <v>1.97</v>
@@ -6133,7 +6139,7 @@
         <v>1.31</v>
       </c>
       <c r="AY31">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AZ31">
         <v>0</v>
@@ -6159,7 +6165,7 @@
         <v>67</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D32" t="s">
         <v>83</v>
@@ -6183,31 +6189,31 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L32">
-        <v>2.01</v>
+        <v>1.61</v>
       </c>
       <c r="M32">
-        <v>3.33</v>
+        <v>3.78</v>
       </c>
       <c r="N32">
-        <v>3.12</v>
+        <v>4.3</v>
       </c>
       <c r="O32">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="P32">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="Q32">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="R32">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S32">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T32">
         <v>2.75</v>
@@ -6216,94 +6222,94 @@
         <v>1.4</v>
       </c>
       <c r="V32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W32">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>8.5</v>
+        <v>10.2</v>
       </c>
       <c r="Z32">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AA32">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="AB32">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC32">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AD32">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AE32">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF32">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AG32">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH32">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="AI32">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AJ32" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK32" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL32">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AM32">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AN32">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AO32">
         <v>-1</v>
       </c>
       <c r="AP32">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AQ32">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR32">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AS32">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="AT32">
-        <v>2.95</v>
+        <v>2.43</v>
       </c>
       <c r="AU32">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AV32">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AW32">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="AX32">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="AY32">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="AZ32">
         <v>0</v>
@@ -6312,10 +6318,10 @@
         <v>0</v>
       </c>
       <c r="BB32">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="BC32">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="BD32" s="3">
         <v>45805.89583333334</v>
@@ -6329,7 +6335,7 @@
         <v>67</v>
       </c>
       <c r="C33" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D33" t="s">
         <v>83</v>
@@ -6353,127 +6359,127 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L33">
-        <v>1.82</v>
+        <v>1.32</v>
       </c>
       <c r="M33">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="N33">
-        <v>3.68</v>
+        <v>6.4</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AB33">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AC33">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH33">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI33">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ33" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK33" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL33">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AM33">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN33">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AO33">
         <v>-1</v>
       </c>
       <c r="AP33">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU33">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV33">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW33">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX33">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AY33">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AZ33">
         <v>0</v>
@@ -6482,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="BB33">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC33">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BD33" s="3">
         <v>45805.89583333334</v>
@@ -6499,7 +6505,7 @@
         <v>67</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D34" t="s">
         <v>83</v>
@@ -6523,127 +6529,127 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L34">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="M34">
-        <v>3.78</v>
+        <v>3.35</v>
       </c>
       <c r="N34">
-        <v>4.3</v>
+        <v>3.68</v>
       </c>
       <c r="O34">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P34">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S34">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y34">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="Z34">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AA34">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AB34">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC34">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AD34">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG34">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH34">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AI34">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK34" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL34">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AM34">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN34">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO34">
         <v>-1</v>
       </c>
       <c r="AP34">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ34">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR34">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AS34">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AT34">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AU34">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AV34">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AW34">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AX34">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY34">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AZ34">
         <v>0</v>
@@ -6652,10 +6658,10 @@
         <v>0</v>
       </c>
       <c r="BB34">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BC34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BD34" s="3">
         <v>45805.89583333334</v>
@@ -6669,7 +6675,7 @@
         <v>67</v>
       </c>
       <c r="C35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
         <v>83</v>
@@ -6693,139 +6699,139 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L35">
-        <v>1.32</v>
+        <v>2.01</v>
       </c>
       <c r="M35">
-        <v>4.9</v>
+        <v>3.33</v>
       </c>
       <c r="N35">
-        <v>6.4</v>
+        <v>3.12</v>
       </c>
       <c r="O35">
+        <v>1.67</v>
+      </c>
+      <c r="P35">
+        <v>9</v>
+      </c>
+      <c r="Q35">
+        <v>2.4</v>
+      </c>
+      <c r="R35">
+        <v>1.36</v>
+      </c>
+      <c r="S35">
+        <v>3</v>
+      </c>
+      <c r="T35">
+        <v>2.75</v>
+      </c>
+      <c r="U35">
+        <v>1.4</v>
+      </c>
+      <c r="V35">
+        <v>7</v>
+      </c>
+      <c r="W35">
+        <v>1.1</v>
+      </c>
+      <c r="X35">
+        <v>1.06</v>
+      </c>
+      <c r="Y35">
+        <v>8.5</v>
+      </c>
+      <c r="Z35">
+        <v>1.3</v>
+      </c>
+      <c r="AA35">
+        <v>3.4</v>
+      </c>
+      <c r="AB35">
+        <v>1.86</v>
+      </c>
+      <c r="AC35">
+        <v>1.84</v>
+      </c>
+      <c r="AD35">
+        <v>3.35</v>
+      </c>
+      <c r="AE35">
+        <v>1.3</v>
+      </c>
+      <c r="AF35">
+        <v>1.75</v>
+      </c>
+      <c r="AG35">
+        <v>2</v>
+      </c>
+      <c r="AH35">
+        <v>6.5</v>
+      </c>
+      <c r="AI35">
+        <v>1.1</v>
+      </c>
+      <c r="AJ35" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK35" t="s">
+        <v>168</v>
+      </c>
+      <c r="AL35">
+        <v>1.28</v>
+      </c>
+      <c r="AM35">
         <v>1.29</v>
       </c>
-      <c r="P35">
-        <v>13</v>
-      </c>
-      <c r="Q35">
-        <v>3.75</v>
-      </c>
-      <c r="R35">
-        <v>1.29</v>
-      </c>
-      <c r="S35">
-        <v>3.5</v>
-      </c>
-      <c r="T35">
-        <v>2.38</v>
-      </c>
-      <c r="U35">
-        <v>1.53</v>
-      </c>
-      <c r="V35">
-        <v>5.5</v>
-      </c>
-      <c r="W35">
-        <v>1.14</v>
-      </c>
-      <c r="X35">
-        <v>1.02</v>
-      </c>
-      <c r="Y35">
-        <v>14.3</v>
-      </c>
-      <c r="Z35">
-        <v>1.13</v>
-      </c>
-      <c r="AA35">
-        <v>4.55</v>
-      </c>
-      <c r="AB35">
-        <v>1.6</v>
-      </c>
-      <c r="AC35">
-        <v>2.1</v>
-      </c>
-      <c r="AD35">
-        <v>2.58</v>
-      </c>
-      <c r="AE35">
-        <v>1.5</v>
-      </c>
-      <c r="AF35">
-        <v>1.91</v>
-      </c>
-      <c r="AG35">
-        <v>1.91</v>
-      </c>
-      <c r="AH35">
-        <v>4.6</v>
-      </c>
-      <c r="AI35">
-        <v>1.14</v>
-      </c>
-      <c r="AJ35" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK35" t="s">
-        <v>166</v>
-      </c>
-      <c r="AL35">
-        <v>1.09</v>
-      </c>
-      <c r="AM35">
-        <v>1.17</v>
-      </c>
       <c r="AN35">
-        <v>2.95</v>
+        <v>1.75</v>
       </c>
       <c r="AO35">
         <v>-1</v>
       </c>
       <c r="AP35">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AQ35">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR35">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AS35">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AT35">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="AU35">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="AV35">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AW35">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AX35">
+        <v>1.54</v>
+      </c>
+      <c r="AY35">
+        <v>1.34</v>
+      </c>
+      <c r="AZ35">
+        <v>0</v>
+      </c>
+      <c r="BA35">
+        <v>0</v>
+      </c>
+      <c r="BB35">
         <v>1.67</v>
       </c>
-      <c r="AY35">
-        <v>1.44</v>
-      </c>
-      <c r="AZ35">
-        <v>0</v>
-      </c>
-      <c r="BA35">
-        <v>0</v>
-      </c>
-      <c r="BB35">
-        <v>1.29</v>
-      </c>
       <c r="BC35">
-        <v>3.75</v>
+        <v>2.4</v>
       </c>
       <c r="BD35" s="3">
         <v>45805.89583333334</v>
@@ -6863,127 +6869,127 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L36">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="M36">
-        <v>12</v>
+        <v>5.6</v>
       </c>
       <c r="N36">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="O36">
+        <v>1.17</v>
+      </c>
+      <c r="P36">
+        <v>13.5</v>
+      </c>
+      <c r="Q36">
+        <v>6</v>
+      </c>
+      <c r="R36">
+        <v>1.29</v>
+      </c>
+      <c r="S36">
+        <v>3.5</v>
+      </c>
+      <c r="T36">
+        <v>2.38</v>
+      </c>
+      <c r="U36">
+        <v>1.53</v>
+      </c>
+      <c r="V36">
+        <v>5.5</v>
+      </c>
+      <c r="W36">
+        <v>1.14</v>
+      </c>
+      <c r="X36">
+        <v>1.03</v>
+      </c>
+      <c r="Y36">
+        <v>13.8</v>
+      </c>
+      <c r="Z36">
+        <v>1.17</v>
+      </c>
+      <c r="AA36">
+        <v>4.2</v>
+      </c>
+      <c r="AB36">
+        <v>1.57</v>
+      </c>
+      <c r="AC36">
+        <v>2.15</v>
+      </c>
+      <c r="AD36">
+        <v>2.75</v>
+      </c>
+      <c r="AE36">
+        <v>1.45</v>
+      </c>
+      <c r="AF36">
+        <v>2.38</v>
+      </c>
+      <c r="AG36">
+        <v>1.53</v>
+      </c>
+      <c r="AH36">
+        <v>4.2</v>
+      </c>
+      <c r="AI36">
+        <v>1.16</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK36" t="s">
+        <v>168</v>
+      </c>
+      <c r="AL36">
+        <v>1.03</v>
+      </c>
+      <c r="AM36">
         <v>1.11</v>
       </c>
-      <c r="P36">
-        <v>0</v>
-      </c>
-      <c r="Q36">
-        <v>6.5</v>
-      </c>
-      <c r="R36">
-        <v>1.17</v>
-      </c>
-      <c r="S36">
-        <v>5</v>
-      </c>
-      <c r="T36">
-        <v>1.8</v>
-      </c>
-      <c r="U36">
-        <v>1.91</v>
-      </c>
-      <c r="V36">
-        <v>3.5</v>
-      </c>
-      <c r="W36">
-        <v>1.29</v>
-      </c>
-      <c r="X36">
-        <v>0</v>
-      </c>
-      <c r="Y36">
-        <v>0</v>
-      </c>
-      <c r="Z36">
-        <v>0</v>
-      </c>
-      <c r="AA36">
-        <v>0</v>
-      </c>
-      <c r="AB36">
-        <v>1.25</v>
-      </c>
-      <c r="AC36">
-        <v>3.5</v>
-      </c>
-      <c r="AD36">
-        <v>1.85</v>
-      </c>
-      <c r="AE36">
-        <v>1.85</v>
-      </c>
-      <c r="AF36">
-        <v>2.63</v>
-      </c>
-      <c r="AG36">
-        <v>1.44</v>
-      </c>
-      <c r="AH36">
-        <v>0</v>
-      </c>
-      <c r="AI36">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK36" t="s">
-        <v>166</v>
-      </c>
-      <c r="AL36">
-        <v>0</v>
-      </c>
-      <c r="AM36">
-        <v>0</v>
-      </c>
       <c r="AN36">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AO36">
         <v>-1</v>
       </c>
       <c r="AP36">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ36">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS36">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT36">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU36">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AV36">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW36">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX36">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY36">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ36">
         <v>0</v>
@@ -6992,10 +6998,10 @@
         <v>0</v>
       </c>
       <c r="BB36">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="BC36">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="BD36" s="3">
         <v>45805.89583333334</v>
@@ -7033,127 +7039,127 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L37">
+        <v>1.02</v>
+      </c>
+      <c r="M37">
+        <v>12</v>
+      </c>
+      <c r="N37">
+        <v>17</v>
+      </c>
+      <c r="O37">
+        <v>1.11</v>
+      </c>
+      <c r="P37">
+        <v>31</v>
+      </c>
+      <c r="Q37">
+        <v>6.5</v>
+      </c>
+      <c r="R37">
         <v>1.17</v>
       </c>
-      <c r="M37">
-        <v>5.6</v>
-      </c>
-      <c r="N37">
+      <c r="S37">
+        <v>5</v>
+      </c>
+      <c r="T37">
+        <v>1.8</v>
+      </c>
+      <c r="U37">
+        <v>1.91</v>
+      </c>
+      <c r="V37">
+        <v>3.5</v>
+      </c>
+      <c r="W37">
+        <v>1.29</v>
+      </c>
+      <c r="X37">
+        <v>1.01</v>
+      </c>
+      <c r="Y37">
         <v>11</v>
       </c>
-      <c r="O37">
-        <v>1.17</v>
-      </c>
-      <c r="P37">
-        <v>13.5</v>
-      </c>
-      <c r="Q37">
-        <v>6</v>
-      </c>
-      <c r="R37">
-        <v>1.29</v>
-      </c>
-      <c r="S37">
-        <v>3.5</v>
-      </c>
-      <c r="T37">
-        <v>2.38</v>
-      </c>
-      <c r="U37">
-        <v>1.53</v>
-      </c>
-      <c r="V37">
-        <v>5.5</v>
-      </c>
-      <c r="W37">
-        <v>1.14</v>
-      </c>
-      <c r="X37">
-        <v>1.03</v>
-      </c>
-      <c r="Y37">
-        <v>13.8</v>
-      </c>
       <c r="Z37">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AA37">
-        <v>4.2</v>
+        <v>7.5</v>
       </c>
       <c r="AB37">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AC37">
-        <v>2.15</v>
+        <v>3.71</v>
       </c>
       <c r="AD37">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="AE37">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="AF37">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AG37">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AH37">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="AI37">
-        <v>1.16</v>
+        <v>1.48</v>
       </c>
       <c r="AJ37" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK37" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL37">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AM37">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AN37">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AO37">
         <v>-1</v>
       </c>
       <c r="AP37">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="AQ37">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="AR37">
-        <v>2.05</v>
+        <v>1.47</v>
       </c>
       <c r="AS37">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="AT37">
+        <v>2.35</v>
+      </c>
+      <c r="AU37">
+        <v>4.4</v>
+      </c>
+      <c r="AV37">
         <v>3.4</v>
       </c>
-      <c r="AU37">
-        <v>2.65</v>
-      </c>
-      <c r="AV37">
-        <v>2.06</v>
-      </c>
       <c r="AW37">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AX37">
-        <v>1.43</v>
+        <v>1.83</v>
       </c>
       <c r="AY37">
-        <v>1.26</v>
+        <v>1.49</v>
       </c>
       <c r="AZ37">
         <v>0</v>
@@ -7162,10 +7168,10 @@
         <v>0</v>
       </c>
       <c r="BB37">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BC37">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="BD37" s="3">
         <v>45805.89583333334</v>
@@ -7203,7 +7209,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L38">
         <v>1.9</v>
@@ -7254,10 +7260,10 @@
         <v>5.25</v>
       </c>
       <c r="AB38">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AC38">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AD38">
         <v>2.15</v>
@@ -7278,10 +7284,10 @@
         <v>1.25</v>
       </c>
       <c r="AJ38" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK38" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL38">
         <v>1.33</v>
@@ -7349,7 +7355,7 @@
         <v>69</v>
       </c>
       <c r="C39" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D39" t="s">
         <v>83</v>
@@ -7373,127 +7379,127 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L39">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="M39">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="N39">
-        <v>2.75</v>
+        <v>3.41</v>
       </c>
       <c r="O39">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="P39">
-        <v>11.25</v>
+        <v>9.75</v>
       </c>
       <c r="Q39">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="R39">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S39">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="T39">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="U39">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V39">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X39">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y39">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="Z39">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AA39">
-        <v>3.14</v>
+        <v>3.7</v>
       </c>
       <c r="AB39">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC39">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AD39">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="AE39">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AF39">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG39">
         <v>2</v>
       </c>
       <c r="AH39">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AI39">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AJ39" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK39" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL39">
+        <v>1.36</v>
+      </c>
+      <c r="AM39">
         <v>1.3</v>
       </c>
-      <c r="AM39">
-        <v>1.27</v>
-      </c>
       <c r="AN39">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AO39">
         <v>-1</v>
       </c>
       <c r="AP39">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ39">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR39">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS39">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT39">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU39">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AV39">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AW39">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX39">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY39">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AZ39">
         <v>0</v>
@@ -7502,10 +7508,10 @@
         <v>0</v>
       </c>
       <c r="BB39">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="BC39">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="BD39" s="3">
         <v>45805.97916666666</v>
@@ -7519,7 +7525,7 @@
         <v>69</v>
       </c>
       <c r="C40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D40" t="s">
         <v>83</v>
@@ -7543,127 +7549,127 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L40">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="M40">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="N40">
-        <v>3.41</v>
+        <v>2.87</v>
       </c>
       <c r="O40">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="P40">
-        <v>9.75</v>
+        <v>11.25</v>
       </c>
       <c r="Q40">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="R40">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S40">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="T40">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="U40">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V40">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="W40">
+        <v>1.08</v>
+      </c>
+      <c r="X40">
+        <v>1</v>
+      </c>
+      <c r="Y40">
+        <v>9.1</v>
+      </c>
+      <c r="Z40">
+        <v>1.27</v>
+      </c>
+      <c r="AA40">
+        <v>3.3</v>
+      </c>
+      <c r="AB40">
+        <v>1.91</v>
+      </c>
+      <c r="AC40">
+        <v>1.79</v>
+      </c>
+      <c r="AD40">
+        <v>3.45</v>
+      </c>
+      <c r="AE40">
+        <v>1.25</v>
+      </c>
+      <c r="AF40">
+        <v>1.76</v>
+      </c>
+      <c r="AG40">
+        <v>1.97</v>
+      </c>
+      <c r="AH40">
+        <v>6</v>
+      </c>
+      <c r="AI40">
         <v>1.1</v>
       </c>
-      <c r="X40">
-        <v>1.05</v>
-      </c>
-      <c r="Y40">
-        <v>9.5</v>
-      </c>
-      <c r="Z40">
-        <v>1.25</v>
-      </c>
-      <c r="AA40">
-        <v>3.7</v>
-      </c>
-      <c r="AB40">
-        <v>1.8</v>
-      </c>
-      <c r="AC40">
-        <v>1.9</v>
-      </c>
-      <c r="AD40">
-        <v>3.1</v>
-      </c>
-      <c r="AE40">
-        <v>1.36</v>
-      </c>
-      <c r="AF40">
-        <v>1.75</v>
-      </c>
-      <c r="AG40">
-        <v>2</v>
-      </c>
-      <c r="AH40">
-        <v>5.75</v>
-      </c>
-      <c r="AI40">
-        <v>1.12</v>
-      </c>
       <c r="AJ40" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK40" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL40">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AM40">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AN40">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AO40">
         <v>-1</v>
       </c>
       <c r="AP40">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="AQ40">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="AR40">
-        <v>1.62</v>
+        <v>2.37</v>
       </c>
       <c r="AS40">
-        <v>1.98</v>
+        <v>2.63</v>
       </c>
       <c r="AT40">
-        <v>2.48</v>
+        <v>3.5</v>
       </c>
       <c r="AU40">
-        <v>3.8</v>
+        <v>2.78</v>
       </c>
       <c r="AV40">
-        <v>2.75</v>
+        <v>2.11</v>
       </c>
       <c r="AW40">
-        <v>2.14</v>
+        <v>1.7</v>
       </c>
       <c r="AX40">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="AY40">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="AZ40">
         <v>0</v>
@@ -7672,10 +7678,10 @@
         <v>0</v>
       </c>
       <c r="BB40">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="BC40">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="BD40" s="3">
         <v>45805.97916666666</v>
@@ -7713,7 +7719,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L41">
         <v>1.6</v>
@@ -7764,10 +7770,10 @@
         <v>5.25</v>
       </c>
       <c r="AB41">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC41">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AD41">
         <v>2.15</v>
@@ -7788,10 +7794,10 @@
         <v>1.25</v>
       </c>
       <c r="AJ41" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AK41" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AL41">
         <v>1.21</v>

--- a/jogos_2025-05-28.xlsx
+++ b/jogos_2025-05-28.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,22 +901,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.94</v>
+        <v>2.71</v>
       </c>
       <c r="M4" t="n">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
       <c r="N4" t="n">
-        <v>3.41</v>
+        <v>2.31</v>
       </c>
       <c r="O4" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
         <v>1.06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="X4" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45805.3125</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,19 +1030,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1056,43 +1056,43 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.59</v>
+        <v>1.94</v>
       </c>
       <c r="M5" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="N5" t="n">
-        <v>2.34</v>
+        <v>3.41</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V5" t="n">
         <v>1.06</v>
       </c>
       <c r="W5" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="X5" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Y5" t="n">
         <v>1.89</v>
@@ -1101,16 +1101,16 @@
         <v>1.81</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1119,20 +1119,20 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="AI5" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45805.3125</v>
@@ -1159,22 +1159,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.71</v>
+        <v>2.59</v>
       </c>
       <c r="M6" t="n">
-        <v>3.14</v>
+        <v>3.27</v>
       </c>
       <c r="N6" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
         <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V6" t="n">
         <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X6" t="n">
         <v>3.1</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['81']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI6" t="n">
         <v>2</v>
       </c>
-      <c r="Z6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['31']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['48']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AJ6" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45805.3125</v>
@@ -1794,119 +1794,119 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P11" t="n">
         <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V11" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['24', '90+3']</t>
+          <t>['15', '24', '61', '83', '85']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45805.58333333334</v>
@@ -2062,109 +2062,109 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O13" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3.9</v>
-      </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.58</v>
+        <v>5.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.65</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.8</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="V13" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X13" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.07</v>
+        <v>1.76</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['22']</t>
+          <t>['14', '59']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['15', '24', '61', '83', '85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.17</v>
+        <v>2.43</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.75</v>
+        <v>1.57</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.57</v>
+        <v>3.1</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45805.58333333334</v>
@@ -2181,119 +2181,119 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
         <v>2</v>
       </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
       <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.76</v>
+        <v>2.72</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N14" t="n">
-        <v>5.25</v>
+        <v>2.25</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.25</v>
+        <v>2.88</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="T14" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W14" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="X14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AA14" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['14', '59']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24', '90+3']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.43</v>
+        <v>1.35</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45805.58333333334</v>
@@ -2965,103 +2965,103 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="H20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.18</v>
+        <v>1.72</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N20" t="n">
-        <v>1.75</v>
+        <v>4.7</v>
       </c>
       <c r="O20" t="n">
-        <v>4.33</v>
+        <v>2.4</v>
       </c>
       <c r="P20" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.3</v>
+        <v>5.05</v>
       </c>
       <c r="R20" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="U20" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="V20" t="n">
         <v>1.04</v>
       </c>
       <c r="W20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X20" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Z20" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AD20" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['75']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['86', '90+2']</t>
+          <t>['25', '50', '90+4']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.17</v>
+        <v>2.1</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
         <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,77 +3120,77 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="O21" t="n">
-        <v>2.97</v>
+        <v>2.26</v>
       </c>
       <c r="P21" t="n">
-        <v>2.16</v>
+        <v>2.58</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="U21" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="Z21" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['14', '29', '70', '90+7']</t>
+          <t>['30', '42', '86']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['26', '76']</t>
+          <t>['50', '68', '90+2']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,109 +3223,109 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>3</v>
       </c>
       <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O22" t="n">
         <v>3</v>
       </c>
-      <c r="I22" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="M22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.26</v>
-      </c>
       <c r="P22" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T22" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="U22" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="V22" t="n">
         <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X22" t="n">
-        <v>5.1</v>
+        <v>4.33</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Z22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD22" t="n">
         <v>2.38</v>
       </c>
-      <c r="AA22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['30', '42', '86']</t>
+          <t>['19', '83', '90+5']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['50', '68', '90+2']</t>
+          <t>['4', '32']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.3</v>
+        <v>1.52</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45805.85416666666</v>
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,46 +3378,46 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.59</v>
+        <v>2.91</v>
       </c>
       <c r="M23" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q23" t="n">
         <v>3</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.3</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="T23" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
         <v>1.05</v>
       </c>
       <c r="W23" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X23" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="Z23" t="n">
         <v>1.87</v>
@@ -3426,35 +3426,35 @@
         <v>3</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['90+1']</t>
+          <t>['75']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>['86', '90+2']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45805.85416666666</v>
@@ -3481,19 +3481,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="M24" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>4.7</v>
+        <v>3.29</v>
       </c>
       <c r="O24" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.05</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.91</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="V24" t="n">
         <v>1.04</v>
       </c>
       <c r="W24" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X24" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['25', '50', '90+4']</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45805.85416666666</v>
@@ -3610,109 +3610,109 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
         <v>2</v>
       </c>
       <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.85</v>
+        <v>1.8</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="N25" t="n">
-        <v>2.62</v>
+        <v>3.71</v>
       </c>
       <c r="O25" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="P25" t="n">
         <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.8</v>
+        <v>4.33</v>
       </c>
       <c r="R25" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="U25" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="X25" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['19', '83', '90+5']</t>
+          <t>['14', '29', '70', '90+7']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['4', '32']</t>
+          <t>['26', '76']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.39</v>
+        <v>1.88</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45805.85416666666</v>
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M26" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q26" t="n">
         <v>6</v>
       </c>
-      <c r="O26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>6.25</v>
-      </c>
       <c r="R26" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U26" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="V26" t="n">
         <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AB26" t="n">
         <v>1.61</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.58</v>
+        <v>2.1</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45805.85416666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G27" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
         <v>2</v>
       </c>
-      <c r="H27" t="n">
-        <v>2</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="M27" t="n">
-        <v>3.66</v>
+        <v>4.3</v>
       </c>
       <c r="N27" t="n">
-        <v>3.5</v>
+        <v>5.68</v>
       </c>
       <c r="O27" t="n">
-        <v>2.48</v>
+        <v>1.85</v>
       </c>
       <c r="P27" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="S27" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="T27" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="U27" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="V27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['69', '81']</t>
+          <t>['5', '17', '54', '90+3']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['2', '78']</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45805.875</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,19 +3997,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U28" t="n">
         <v>1.6</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="N28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.68</v>
-      </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="AA28" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['72', '78']</t>
+          <t>['69', '81']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['18', '62', '90']</t>
+          <t>['2', '78']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45805.875</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,109 +4126,109 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="H29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="M29" t="n">
-        <v>3.41</v>
+        <v>3.94</v>
       </c>
       <c r="N29" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
-        <v>2.72</v>
+        <v>2</v>
       </c>
       <c r="P29" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="R29" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="S29" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="T29" t="n">
-        <v>3.02</v>
+        <v>2.09</v>
       </c>
       <c r="U29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>['72', '78']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>['18', '62', '90']</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI29" t="n">
         <v>1.33</v>
       </c>
-      <c r="V29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>['45+4']</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>['70']</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ29" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45805.875</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,22 +4255,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -4281,65 +4281,65 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.47</v>
+        <v>2.2</v>
       </c>
       <c r="M30" t="n">
-        <v>4.3</v>
+        <v>3.41</v>
       </c>
       <c r="N30" t="n">
-        <v>5.68</v>
+        <v>2.9</v>
       </c>
       <c r="O30" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD30" t="n">
         <v>1.85</v>
       </c>
-      <c r="P30" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['5', '17', '54', '90+3']</t>
+          <t>['45+4']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.45</v>
+        <v>1.64</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45805.875</v>
@@ -4642,22 +4642,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Sporting Cristal</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4668,22 +4668,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="M33" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="N33" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="O33" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="P33" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R33" t="n">
         <v>1.29</v>
@@ -4698,35 +4698,35 @@
         <v>1.53</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W33" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X33" t="n">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['41', '45+2', '50', '80']</t>
+          <t>['32', '39', '45+2', '64', '71', '80']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.95</v>
+        <v>4.2</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AJ33" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45805.89583333334</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,22 +4771,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4797,65 +4797,65 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.82</v>
+        <v>1.32</v>
       </c>
       <c r="M34" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="N34" t="n">
-        <v>3.68</v>
+        <v>6.4</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['41', '45+2', '50', '80']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45805.89583333334</v>
@@ -4900,22 +4900,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sporting Cristal</t>
+          <t>Deportivo Táchira</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4926,65 +4926,65 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="M35" t="n">
+        <v>12</v>
+      </c>
+      <c r="N35" t="n">
+        <v>17</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>19</v>
+      </c>
+      <c r="R35" t="n">
         <v>1.17</v>
       </c>
-      <c r="M35" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N35" t="n">
-        <v>11</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>12</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.29</v>
-      </c>
       <c r="S35" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="T35" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="U35" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="V35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X35" t="n">
-        <v>4.2</v>
+        <v>7.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.15</v>
+        <v>3.71</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['32', '39', '45+2', '64', '71', '80']</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AH35" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AJ35" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45805.89583333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Deportivo Táchira</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,65 +5055,65 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.02</v>
+        <v>1.82</v>
       </c>
       <c r="M36" t="n">
-        <v>12</v>
+        <v>3.35</v>
       </c>
       <c r="N36" t="n">
-        <v>17</v>
+        <v>3.68</v>
       </c>
       <c r="O36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.71</v>
+        <v>1.87</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45805.89583333334</v>
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="M38" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q38" t="n">
         <v>3.6</v>
       </c>
-      <c r="N38" t="n">
-        <v>3</v>
-      </c>
-      <c r="O38" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>3.65</v>
-      </c>
       <c r="R38" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S38" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="T38" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="U38" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="V38" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X38" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB38" t="n">
         <v>1.65</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,16 +5380,16 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45805.96875</v>
@@ -5416,25 +5416,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5442,77 +5442,77 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.6</v>
+        <v>2.27</v>
       </c>
       <c r="M39" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>5.25</v>
+        <v>2.98</v>
       </c>
       <c r="O39" t="n">
-        <v>2.17</v>
+        <v>2.77</v>
       </c>
       <c r="P39" t="n">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.55</v>
+        <v>3.55</v>
       </c>
       <c r="R39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
         <v>1.25</v>
       </c>
-      <c r="S39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X39" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>['59', '76']</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>['33']</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH39" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,25 +5545,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5571,77 +5571,77 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.27</v>
+        <v>1.6</v>
       </c>
       <c r="M40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N40" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S40" t="n">
         <v>3.5</v>
       </c>
-      <c r="N40" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O40" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="P40" t="n">
+      <c r="T40" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q40" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.6</v>
-      </c>
       <c r="U40" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="V40" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W40" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="X40" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.87</v>
+        <v>2.37</v>
       </c>
       <c r="AA40" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.33</v>
+        <v>1.69</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['59', '76']</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
